--- a/research/traditional_assets/database/data/lithuania/lithuania_oil_gas_distribution.xlsx
+++ b/research/traditional_assets/database/data/lithuania/lithuania_oil_gas_distribution.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07670915467234131</v>
+        <v>0.07663234094033279</v>
       </c>
       <c r="C2">
-        <v>503.233956070172</v>
+        <v>499.4212909827916</v>
       </c>
       <c r="D2">
-        <v>477.433956070172</v>
+        <v>478.5692909827916</v>
       </c>
       <c r="E2">
-        <v>-401.5</v>
+        <v>-396.552</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4.948</v>
       </c>
       <c r="G2">
         <v>25.8</v>
@@ -1445,28 +1445,28 @@
         <v>38.95</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2488844</v>
       </c>
       <c r="N2">
-        <v>38.95</v>
+        <v>38.7011156</v>
       </c>
       <c r="O2">
-        <v>5.8425</v>
+        <v>5.80516734</v>
       </c>
       <c r="P2">
-        <v>33.1075</v>
+        <v>32.89594826</v>
       </c>
       <c r="Q2">
-        <v>35.6575</v>
+        <v>35.44594826</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07670915467234131</v>
+        <v>0.07697453630336645</v>
       </c>
       <c r="T2">
-        <v>0.5661120226706917</v>
+        <v>0.5709725804410966</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>156.4983582739617</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07663234094033279</v>
+        <v>0.07655552720832427</v>
       </c>
       <c r="C3">
-        <v>499.4212909827916</v>
+        <v>495.6140384047341</v>
       </c>
       <c r="D3">
-        <v>478.5692909827916</v>
+        <v>479.7100384047341</v>
       </c>
       <c r="E3">
-        <v>-396.552</v>
+        <v>-391.604</v>
       </c>
       <c r="F3">
-        <v>4.948</v>
+        <v>9.896000000000001</v>
       </c>
       <c r="G3">
         <v>25.8</v>
@@ -1527,28 +1527,28 @@
         <v>38.95</v>
       </c>
       <c r="M3">
-        <v>0.2488844</v>
+        <v>0.4977688</v>
       </c>
       <c r="N3">
-        <v>38.7011156</v>
+        <v>38.4522312</v>
       </c>
       <c r="O3">
-        <v>5.80516734</v>
+        <v>5.76783468</v>
       </c>
       <c r="P3">
-        <v>32.89594826</v>
+        <v>32.68439652</v>
       </c>
       <c r="Q3">
-        <v>35.44594826</v>
+        <v>35.23439652</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07697453630336645</v>
+        <v>0.07724533388604518</v>
       </c>
       <c r="T3">
-        <v>0.5709725804410966</v>
+        <v>0.5759323332680405</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>156.4983582739617</v>
+        <v>78.24917913698086</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07655552720832427</v>
+        <v>0.07647871347631575</v>
       </c>
       <c r="C4">
-        <v>495.6140384047341</v>
+        <v>491.8122371332575</v>
       </c>
       <c r="D4">
-        <v>479.7100384047341</v>
+        <v>480.8562371332575</v>
       </c>
       <c r="E4">
-        <v>-391.604</v>
+        <v>-386.656</v>
       </c>
       <c r="F4">
-        <v>9.896000000000001</v>
+        <v>14.844</v>
       </c>
       <c r="G4">
         <v>25.8</v>
@@ -1609,28 +1609,28 @@
         <v>38.95</v>
       </c>
       <c r="M4">
-        <v>0.4977688</v>
+        <v>0.7466531999999999</v>
       </c>
       <c r="N4">
-        <v>38.4522312</v>
+        <v>38.20334680000001</v>
       </c>
       <c r="O4">
-        <v>5.76783468</v>
+        <v>5.73050202</v>
       </c>
       <c r="P4">
-        <v>32.68439652</v>
+        <v>32.47284478</v>
       </c>
       <c r="Q4">
-        <v>35.23439652</v>
+        <v>35.02284478</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07724533388604518</v>
+        <v>0.07752171492403687</v>
       </c>
       <c r="T4">
-        <v>0.5759323332680405</v>
+        <v>0.5809943490398697</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>78.24917913698086</v>
+        <v>52.16611942465392</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07647871347631575</v>
+        <v>0.07640189974430724</v>
       </c>
       <c r="C5">
-        <v>491.8122371332575</v>
+        <v>488.0159263373093</v>
       </c>
       <c r="D5">
-        <v>480.8562371332575</v>
+        <v>482.0079263373093</v>
       </c>
       <c r="E5">
-        <v>-386.656</v>
+        <v>-381.708</v>
       </c>
       <c r="F5">
-        <v>14.844</v>
+        <v>19.792</v>
       </c>
       <c r="G5">
         <v>25.8</v>
@@ -1691,28 +1691,28 @@
         <v>38.95</v>
       </c>
       <c r="M5">
-        <v>0.7466531999999999</v>
+        <v>0.9955376</v>
       </c>
       <c r="N5">
-        <v>38.20334680000001</v>
+        <v>37.9544624</v>
       </c>
       <c r="O5">
-        <v>5.73050202</v>
+        <v>5.693169360000001</v>
       </c>
       <c r="P5">
-        <v>32.47284478</v>
+        <v>32.26129304000001</v>
       </c>
       <c r="Q5">
-        <v>35.02284478</v>
+        <v>34.81129304</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07752171492403687</v>
+        <v>0.07780385390032005</v>
       </c>
       <c r="T5">
-        <v>0.5809943490398697</v>
+        <v>0.586161823473612</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>52.16611942465392</v>
+        <v>39.12458956849044</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07640189974430724</v>
+        <v>0.07632508601229873</v>
       </c>
       <c r="C6">
-        <v>488.0159263373093</v>
+        <v>484.2251455619889</v>
       </c>
       <c r="D6">
-        <v>482.0079263373093</v>
+        <v>483.1651455619889</v>
       </c>
       <c r="E6">
-        <v>-381.708</v>
+        <v>-376.76</v>
       </c>
       <c r="F6">
-        <v>19.792</v>
+        <v>24.74</v>
       </c>
       <c r="G6">
         <v>25.8</v>
@@ -1773,28 +1773,28 @@
         <v>38.95</v>
       </c>
       <c r="M6">
-        <v>0.9955376</v>
+        <v>1.244422</v>
       </c>
       <c r="N6">
-        <v>37.9544624</v>
+        <v>37.705578</v>
       </c>
       <c r="O6">
-        <v>5.693169360000001</v>
+        <v>5.6558367</v>
       </c>
       <c r="P6">
-        <v>32.26129304000001</v>
+        <v>32.0497413</v>
       </c>
       <c r="Q6">
-        <v>34.81129304</v>
+        <v>34.5997413</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07780385390032005</v>
+        <v>0.07809193264452499</v>
       </c>
       <c r="T6">
-        <v>0.586161823473612</v>
+        <v>0.5914380868428016</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>39.12458956849044</v>
+        <v>31.29967165479234</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07632508601229873</v>
+        <v>0.07624827228029024</v>
       </c>
       <c r="C7">
-        <v>484.2251455619889</v>
+        <v>480.4399347330746</v>
       </c>
       <c r="D7">
-        <v>483.1651455619889</v>
+        <v>484.3279347330745</v>
       </c>
       <c r="E7">
-        <v>-376.76</v>
+        <v>-371.812</v>
       </c>
       <c r="F7">
-        <v>24.74</v>
+        <v>29.688</v>
       </c>
       <c r="G7">
         <v>25.8</v>
@@ -1855,28 +1855,28 @@
         <v>38.95</v>
       </c>
       <c r="M7">
-        <v>1.244422</v>
+        <v>1.4933064</v>
       </c>
       <c r="N7">
-        <v>37.705578</v>
+        <v>37.4566936</v>
       </c>
       <c r="O7">
-        <v>5.6558367</v>
+        <v>5.61850404</v>
       </c>
       <c r="P7">
-        <v>32.0497413</v>
+        <v>31.83818956</v>
       </c>
       <c r="Q7">
-        <v>34.5997413</v>
+        <v>34.38818956</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07809193264452499</v>
+        <v>0.07838614072371301</v>
       </c>
       <c r="T7">
-        <v>0.5914380868428016</v>
+        <v>0.5968266111347399</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>31.29967165479234</v>
+        <v>26.08305971232695</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07624827228029024</v>
+        <v>0.07617145854828174</v>
       </c>
       <c r="C8">
-        <v>480.4399347330746</v>
+        <v>476.6603341616143</v>
       </c>
       <c r="D8">
-        <v>484.3279347330745</v>
+        <v>485.4963341616143</v>
       </c>
       <c r="E8">
-        <v>-371.812</v>
+        <v>-366.864</v>
       </c>
       <c r="F8">
-        <v>29.688</v>
+        <v>34.636</v>
       </c>
       <c r="G8">
         <v>25.8</v>
@@ -1937,28 +1937,28 @@
         <v>38.95</v>
       </c>
       <c r="M8">
-        <v>1.4933064</v>
+        <v>1.7421908</v>
       </c>
       <c r="N8">
-        <v>37.4566936</v>
+        <v>37.2078092</v>
       </c>
       <c r="O8">
-        <v>5.61850404</v>
+        <v>5.58117138</v>
       </c>
       <c r="P8">
-        <v>31.83818956</v>
+        <v>31.62663782</v>
       </c>
       <c r="Q8">
-        <v>34.38818956</v>
+        <v>34.17663782</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07838614072371301</v>
+        <v>0.07868667585836744</v>
       </c>
       <c r="T8">
-        <v>0.5968266111347399</v>
+        <v>0.6023310176695156</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>26.08305971232696</v>
+        <v>22.35690832485168</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07617145854828172</v>
+        <v>0.07609464481627322</v>
       </c>
       <c r="C9">
-        <v>476.6603341616145</v>
+        <v>472.8863845485845</v>
       </c>
       <c r="D9">
-        <v>485.4963341616145</v>
+        <v>486.6703845485846</v>
       </c>
       <c r="E9">
-        <v>-366.864</v>
+        <v>-361.916</v>
       </c>
       <c r="F9">
-        <v>34.636</v>
+        <v>39.584</v>
       </c>
       <c r="G9">
         <v>25.8</v>
@@ -2019,28 +2019,28 @@
         <v>38.95</v>
       </c>
       <c r="M9">
-        <v>1.7421908</v>
+        <v>1.9910752</v>
       </c>
       <c r="N9">
-        <v>37.2078092</v>
+        <v>36.95892480000001</v>
       </c>
       <c r="O9">
-        <v>5.58117138</v>
+        <v>5.543838720000001</v>
       </c>
       <c r="P9">
-        <v>31.62663782</v>
+        <v>31.41508608000001</v>
       </c>
       <c r="Q9">
-        <v>34.17663782</v>
+        <v>33.96508608000001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07868667585836744</v>
+        <v>0.07899374436551436</v>
       </c>
       <c r="T9">
-        <v>0.6023310176695156</v>
+        <v>0.6079550852159168</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>22.35690832485167</v>
+        <v>19.56229478424522</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07609464481627322</v>
+        <v>0.0760178310842647</v>
       </c>
       <c r="C10">
-        <v>472.8863845485845</v>
+        <v>469.1181269896162</v>
       </c>
       <c r="D10">
-        <v>486.6703845485846</v>
+        <v>487.8501269896162</v>
       </c>
       <c r="E10">
-        <v>-361.916</v>
+        <v>-356.968</v>
       </c>
       <c r="F10">
-        <v>39.584</v>
+        <v>44.532</v>
       </c>
       <c r="G10">
         <v>25.8</v>
@@ -2101,28 +2101,28 @@
         <v>38.95</v>
       </c>
       <c r="M10">
-        <v>1.9910752</v>
+        <v>2.2399596</v>
       </c>
       <c r="N10">
-        <v>36.95892480000001</v>
+        <v>36.7100404</v>
       </c>
       <c r="O10">
-        <v>5.543838720000001</v>
+        <v>5.50650606</v>
       </c>
       <c r="P10">
-        <v>31.41508608000001</v>
+        <v>31.20353434</v>
       </c>
       <c r="Q10">
-        <v>33.96508608000001</v>
+        <v>33.75353434</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07899374436551436</v>
+        <v>0.07930756163106011</v>
       </c>
       <c r="T10">
-        <v>0.6079550852159168</v>
+        <v>0.6137027586424586</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>19.56229478424522</v>
+        <v>17.38870647488464</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0760178310842647</v>
+        <v>0.07594101735225618</v>
       </c>
       <c r="C11">
-        <v>469.1181269896162</v>
+        <v>465.3556029797892</v>
       </c>
       <c r="D11">
-        <v>487.8501269896162</v>
+        <v>489.0356029797892</v>
       </c>
       <c r="E11">
-        <v>-356.968</v>
+        <v>-352.02</v>
       </c>
       <c r="F11">
-        <v>44.532</v>
+        <v>49.48</v>
       </c>
       <c r="G11">
         <v>25.8</v>
@@ -2183,28 +2183,28 @@
         <v>38.95</v>
       </c>
       <c r="M11">
-        <v>2.2399596</v>
+        <v>2.488844</v>
       </c>
       <c r="N11">
-        <v>36.7100404</v>
+        <v>36.461156</v>
       </c>
       <c r="O11">
-        <v>5.50650606</v>
+        <v>5.4691734</v>
       </c>
       <c r="P11">
-        <v>31.20353434</v>
+        <v>30.9919826</v>
       </c>
       <c r="Q11">
-        <v>33.75353434</v>
+        <v>33.5419826</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07930756163106011</v>
+        <v>0.07962835261361798</v>
       </c>
       <c r="T11">
-        <v>0.6137027586424586</v>
+        <v>0.6195781581451459</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>17.38870647488464</v>
+        <v>15.64983582739617</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07594101735225618</v>
+        <v>0.07586420362024768</v>
       </c>
       <c r="C12">
-        <v>465.3556029797892</v>
+        <v>461.5988544184991</v>
       </c>
       <c r="D12">
-        <v>489.0356029797892</v>
+        <v>490.2268544184991</v>
       </c>
       <c r="E12">
-        <v>-352.02</v>
+        <v>-347.072</v>
       </c>
       <c r="F12">
-        <v>49.48</v>
+        <v>54.428</v>
       </c>
       <c r="G12">
         <v>25.8</v>
@@ -2265,28 +2265,28 @@
         <v>38.95</v>
       </c>
       <c r="M12">
-        <v>2.488844</v>
+        <v>2.7377284</v>
       </c>
       <c r="N12">
-        <v>36.461156</v>
+        <v>36.2122716</v>
       </c>
       <c r="O12">
-        <v>5.4691734</v>
+        <v>5.43184074</v>
       </c>
       <c r="P12">
-        <v>30.9919826</v>
+        <v>30.78043086</v>
       </c>
       <c r="Q12">
-        <v>33.5419826</v>
+        <v>33.33043086</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07962835261361798</v>
+        <v>0.07995635238230075</v>
       </c>
       <c r="T12">
-        <v>0.6195781581451459</v>
+        <v>0.6255855890973319</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.64983582739617</v>
+        <v>14.22712347945107</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07586420362024768</v>
+        <v>0.07578738988823916</v>
       </c>
       <c r="C13">
-        <v>461.5988544184991</v>
+        <v>457.8479236143924</v>
       </c>
       <c r="D13">
-        <v>490.2268544184991</v>
+        <v>491.4239236143923</v>
       </c>
       <c r="E13">
-        <v>-347.072</v>
+        <v>-342.124</v>
       </c>
       <c r="F13">
-        <v>54.428</v>
+        <v>59.376</v>
       </c>
       <c r="G13">
         <v>25.8</v>
@@ -2347,28 +2347,28 @@
         <v>38.95</v>
       </c>
       <c r="M13">
-        <v>2.7377284</v>
+        <v>2.9866128</v>
       </c>
       <c r="N13">
-        <v>36.2122716</v>
+        <v>35.9633872</v>
       </c>
       <c r="O13">
-        <v>5.43184074</v>
+        <v>5.39450808</v>
       </c>
       <c r="P13">
-        <v>30.78043086</v>
+        <v>30.56887912</v>
       </c>
       <c r="Q13">
-        <v>33.33043086</v>
+        <v>33.11887912</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07995635238230075</v>
+        <v>0.08029180669118086</v>
       </c>
       <c r="T13">
-        <v>0.6255855890973319</v>
+        <v>0.6317295525711583</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>14.22712347945107</v>
+        <v>13.04152985616348</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07578738988823916</v>
+        <v>0.07587632615623063</v>
       </c>
       <c r="C14">
-        <v>457.8479236143924</v>
+        <v>451.5144687978284</v>
       </c>
       <c r="D14">
-        <v>491.4239236143923</v>
+        <v>490.0384687978284</v>
       </c>
       <c r="E14">
-        <v>-342.124</v>
+        <v>-337.176</v>
       </c>
       <c r="F14">
-        <v>59.376</v>
+        <v>64.324</v>
       </c>
       <c r="G14">
         <v>25.8</v>
@@ -2429,45 +2429,45 @@
         <v>38.95</v>
       </c>
       <c r="M14">
-        <v>2.9866128</v>
+        <v>3.3319832</v>
       </c>
       <c r="N14">
-        <v>35.9633872</v>
+        <v>35.61801680000001</v>
       </c>
       <c r="O14">
-        <v>5.39450808</v>
+        <v>5.34270252</v>
       </c>
       <c r="P14">
-        <v>30.56887912</v>
+        <v>30.27531428000001</v>
       </c>
       <c r="Q14">
-        <v>33.11887912</v>
+        <v>32.82531428000001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08029180669118086</v>
+        <v>0.08063497259336855</v>
       </c>
       <c r="T14">
-        <v>0.6317295525711583</v>
+        <v>0.6380147565846128</v>
       </c>
       <c r="U14">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V14">
         <v>0.15</v>
       </c>
       <c r="W14">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y14">
-        <v>13.04152985616348</v>
+        <v>11.68973481018752</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07587632615623063</v>
+        <v>0.07581226242422212</v>
       </c>
       <c r="C15">
-        <v>451.5144687978284</v>
+        <v>447.563669202118</v>
       </c>
       <c r="D15">
-        <v>490.0384687978284</v>
+        <v>491.035669202118</v>
       </c>
       <c r="E15">
-        <v>-337.176</v>
+        <v>-332.228</v>
       </c>
       <c r="F15">
-        <v>64.324</v>
+        <v>69.27200000000001</v>
       </c>
       <c r="G15">
         <v>25.8</v>
@@ -2511,28 +2511,28 @@
         <v>38.95</v>
       </c>
       <c r="M15">
-        <v>3.3319832</v>
+        <v>3.5882896</v>
       </c>
       <c r="N15">
-        <v>35.61801680000001</v>
+        <v>35.3617104</v>
       </c>
       <c r="O15">
-        <v>5.34270252</v>
+        <v>5.30425656</v>
       </c>
       <c r="P15">
-        <v>30.27531428000001</v>
+        <v>30.05745384</v>
       </c>
       <c r="Q15">
-        <v>32.82531428000001</v>
+        <v>32.60745384</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08063497259336855</v>
+        <v>0.08098611909793271</v>
       </c>
       <c r="T15">
-        <v>0.6380147565846128</v>
+        <v>0.6444461281332641</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.68973481018752</v>
+        <v>10.85475375231698</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07581226242422212</v>
+        <v>0.07574819869221361</v>
       </c>
       <c r="C16">
-        <v>447.563669202118</v>
+        <v>443.6169363742267</v>
       </c>
       <c r="D16">
-        <v>491.035669202118</v>
+        <v>492.0369363742268</v>
       </c>
       <c r="E16">
-        <v>-332.228</v>
+        <v>-327.28</v>
       </c>
       <c r="F16">
-        <v>69.27200000000001</v>
+        <v>74.22000000000001</v>
       </c>
       <c r="G16">
         <v>25.8</v>
@@ -2593,28 +2593,28 @@
         <v>38.95</v>
       </c>
       <c r="M16">
-        <v>3.5882896</v>
+        <v>3.844596000000001</v>
       </c>
       <c r="N16">
-        <v>35.3617104</v>
+        <v>35.105404</v>
       </c>
       <c r="O16">
-        <v>5.30425656</v>
+        <v>5.2658106</v>
       </c>
       <c r="P16">
-        <v>30.05745384</v>
+        <v>29.8395934</v>
       </c>
       <c r="Q16">
-        <v>32.60745384</v>
+        <v>32.3895934</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08098611909793271</v>
+        <v>0.08134552787319249</v>
       </c>
       <c r="T16">
-        <v>0.6444461281332641</v>
+        <v>0.6510288260712954</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>10.85475375231698</v>
+        <v>10.13110350216251</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07574819869221361</v>
+        <v>0.07591533496020512</v>
       </c>
       <c r="C17">
-        <v>443.6169363742267</v>
+        <v>436.0652487934404</v>
       </c>
       <c r="D17">
-        <v>492.0369363742268</v>
+        <v>489.4332487934405</v>
       </c>
       <c r="E17">
-        <v>-327.28</v>
+        <v>-322.332</v>
       </c>
       <c r="F17">
-        <v>74.22</v>
+        <v>79.16800000000001</v>
       </c>
       <c r="G17">
         <v>25.8</v>
@@ -2675,45 +2675,45 @@
         <v>38.95</v>
       </c>
       <c r="M17">
-        <v>3.844596</v>
+        <v>4.235488</v>
       </c>
       <c r="N17">
-        <v>35.105404</v>
+        <v>34.714512</v>
       </c>
       <c r="O17">
-        <v>5.2658106</v>
+        <v>5.2071768</v>
       </c>
       <c r="P17">
-        <v>29.8395934</v>
+        <v>29.5073352</v>
       </c>
       <c r="Q17">
-        <v>32.3895934</v>
+        <v>32.0573352</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08134552787319249</v>
+        <v>0.08171349400024419</v>
       </c>
       <c r="T17">
-        <v>0.6510288260712954</v>
+        <v>0.6577682549126133</v>
       </c>
       <c r="U17">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V17">
         <v>0.15</v>
       </c>
       <c r="W17">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>10.13110350216252</v>
+        <v>9.196106800444246</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07591533496020512</v>
+        <v>0.0758657212281966</v>
       </c>
       <c r="C18">
-        <v>436.0652487934404</v>
+        <v>431.8872626833271</v>
       </c>
       <c r="D18">
-        <v>489.4332487934405</v>
+        <v>490.2032626833271</v>
       </c>
       <c r="E18">
-        <v>-322.332</v>
+        <v>-317.384</v>
       </c>
       <c r="F18">
-        <v>79.16800000000001</v>
+        <v>84.11600000000001</v>
       </c>
       <c r="G18">
         <v>25.8</v>
@@ -2757,28 +2757,28 @@
         <v>38.95</v>
       </c>
       <c r="M18">
-        <v>4.235488</v>
+        <v>4.500206</v>
       </c>
       <c r="N18">
-        <v>34.714512</v>
+        <v>34.449794</v>
       </c>
       <c r="O18">
-        <v>5.2071768</v>
+        <v>5.167469100000001</v>
       </c>
       <c r="P18">
-        <v>29.5073352</v>
+        <v>29.2823249</v>
       </c>
       <c r="Q18">
-        <v>32.0573352</v>
+        <v>31.8323249</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08171349400024419</v>
+        <v>0.08209032678095976</v>
       </c>
       <c r="T18">
-        <v>0.6577682549126133</v>
+        <v>0.6646700796296254</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>9.196106800444246</v>
+        <v>8.655159341594585</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0758657212281966</v>
+        <v>0.07581610749618808</v>
       </c>
       <c r="C19">
-        <v>431.8872626833271</v>
+        <v>427.7117032808036</v>
       </c>
       <c r="D19">
-        <v>490.2032626833271</v>
+        <v>490.9757032808037</v>
       </c>
       <c r="E19">
-        <v>-317.384</v>
+        <v>-312.436</v>
       </c>
       <c r="F19">
-        <v>84.11600000000001</v>
+        <v>89.06400000000001</v>
       </c>
       <c r="G19">
         <v>25.8</v>
@@ -2839,28 +2839,28 @@
         <v>38.95</v>
       </c>
       <c r="M19">
-        <v>4.500206</v>
+        <v>4.764924000000001</v>
       </c>
       <c r="N19">
-        <v>34.449794</v>
+        <v>34.185076</v>
       </c>
       <c r="O19">
-        <v>5.167469100000001</v>
+        <v>5.1277614</v>
       </c>
       <c r="P19">
-        <v>29.2823249</v>
+        <v>29.0573146</v>
       </c>
       <c r="Q19">
-        <v>31.8323249</v>
+        <v>31.6073146</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08209032678095976</v>
+        <v>0.08247635060510743</v>
       </c>
       <c r="T19">
-        <v>0.6646700796296254</v>
+        <v>0.6717402415348573</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.655159341594585</v>
+        <v>8.17431715595044</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0758161074961881</v>
+        <v>0.07576649376417958</v>
       </c>
       <c r="C20">
-        <v>427.7117032808036</v>
+        <v>423.5385820756707</v>
       </c>
       <c r="D20">
-        <v>490.9757032808035</v>
+        <v>491.7505820756707</v>
       </c>
       <c r="E20">
-        <v>-312.436</v>
+        <v>-307.488</v>
       </c>
       <c r="F20">
-        <v>89.06399999999999</v>
+        <v>94.012</v>
       </c>
       <c r="G20">
         <v>25.8</v>
@@ -2921,28 +2921,28 @@
         <v>38.95</v>
       </c>
       <c r="M20">
-        <v>4.764924</v>
+        <v>5.029642</v>
       </c>
       <c r="N20">
-        <v>34.185076</v>
+        <v>33.920358</v>
       </c>
       <c r="O20">
-        <v>5.1277614</v>
+        <v>5.0880537</v>
       </c>
       <c r="P20">
-        <v>29.0573146</v>
+        <v>28.8323043</v>
       </c>
       <c r="Q20">
-        <v>31.6073146</v>
+        <v>31.3823043</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08247635060510743</v>
+        <v>0.08287190588170318</v>
       </c>
       <c r="T20">
-        <v>0.6717402415348573</v>
+        <v>0.6789849753389839</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.174317155950442</v>
+        <v>7.744089937216208</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07576649376417958</v>
+        <v>0.07585288003217107</v>
       </c>
       <c r="C21">
-        <v>423.5385820756707</v>
+        <v>417.2429551805546</v>
       </c>
       <c r="D21">
-        <v>491.7505820756707</v>
+        <v>490.4029551805547</v>
       </c>
       <c r="E21">
-        <v>-307.488</v>
+        <v>-302.54</v>
       </c>
       <c r="F21">
-        <v>94.012</v>
+        <v>98.96000000000001</v>
       </c>
       <c r="G21">
         <v>25.8</v>
@@ -3003,45 +3003,45 @@
         <v>38.95</v>
       </c>
       <c r="M21">
-        <v>5.029642</v>
+        <v>5.373528</v>
       </c>
       <c r="N21">
-        <v>33.920358</v>
+        <v>33.576472</v>
       </c>
       <c r="O21">
-        <v>5.0880537</v>
+        <v>5.0364708</v>
       </c>
       <c r="P21">
-        <v>28.8323043</v>
+        <v>28.5400012</v>
       </c>
       <c r="Q21">
-        <v>31.3823043</v>
+        <v>31.0900012</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08287190588170318</v>
+        <v>0.08327735004021383</v>
       </c>
       <c r="T21">
-        <v>0.6789849753389839</v>
+        <v>0.6864108274882137</v>
       </c>
       <c r="U21">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V21">
         <v>0.15</v>
       </c>
       <c r="W21">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y21">
-        <v>7.744089937216208</v>
+        <v>7.248496704585889</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07585288003217107</v>
+        <v>0.07581006630016254</v>
       </c>
       <c r="C22">
-        <v>417.2429551805546</v>
+        <v>412.9619254856397</v>
       </c>
       <c r="D22">
-        <v>490.4029551805547</v>
+        <v>491.0699254856397</v>
       </c>
       <c r="E22">
-        <v>-302.54</v>
+        <v>-297.592</v>
       </c>
       <c r="F22">
-        <v>98.96000000000001</v>
+        <v>103.908</v>
       </c>
       <c r="G22">
         <v>25.8</v>
@@ -3085,28 +3085,28 @@
         <v>38.95</v>
       </c>
       <c r="M22">
-        <v>5.373528</v>
+        <v>5.642204400000001</v>
       </c>
       <c r="N22">
-        <v>33.576472</v>
+        <v>33.30779560000001</v>
       </c>
       <c r="O22">
-        <v>5.0364708</v>
+        <v>4.996169340000001</v>
       </c>
       <c r="P22">
-        <v>28.5400012</v>
+        <v>28.31162626</v>
       </c>
       <c r="Q22">
-        <v>31.0900012</v>
+        <v>30.86162626</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08327735004021383</v>
+        <v>0.0836930586078007</v>
       </c>
       <c r="T22">
-        <v>0.6864108274882137</v>
+        <v>0.694024675894386</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.248496704585889</v>
+        <v>6.903330194843703</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07581006630016254</v>
+        <v>0.07576725256815404</v>
       </c>
       <c r="C23">
-        <v>412.9619254856397</v>
+        <v>408.6827124813559</v>
       </c>
       <c r="D23">
-        <v>491.0699254856397</v>
+        <v>491.7387124813559</v>
       </c>
       <c r="E23">
-        <v>-297.592</v>
+        <v>-292.644</v>
       </c>
       <c r="F23">
-        <v>103.908</v>
+        <v>108.856</v>
       </c>
       <c r="G23">
         <v>25.8</v>
@@ -3167,28 +3167,28 @@
         <v>38.95</v>
       </c>
       <c r="M23">
-        <v>5.6422044</v>
+        <v>5.9108808</v>
       </c>
       <c r="N23">
-        <v>33.30779560000001</v>
+        <v>33.0391192</v>
       </c>
       <c r="O23">
-        <v>4.996169340000001</v>
+        <v>4.95586788</v>
       </c>
       <c r="P23">
-        <v>28.31162626</v>
+        <v>28.08325132</v>
       </c>
       <c r="Q23">
-        <v>30.86162626</v>
+        <v>30.63325132</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08369305860780069</v>
+        <v>0.08411942636942826</v>
       </c>
       <c r="T23">
-        <v>0.6940246758943859</v>
+        <v>0.7018337511827678</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.903330194843704</v>
+        <v>6.589542458714444</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07576725256815404</v>
+        <v>0.07572443883614553</v>
       </c>
       <c r="C24">
-        <v>408.6827124813559</v>
+        <v>404.4053236002668</v>
       </c>
       <c r="D24">
-        <v>491.7387124813559</v>
+        <v>492.4093236002668</v>
       </c>
       <c r="E24">
-        <v>-292.644</v>
+        <v>-287.696</v>
       </c>
       <c r="F24">
-        <v>108.856</v>
+        <v>113.804</v>
       </c>
       <c r="G24">
         <v>25.8</v>
@@ -3249,28 +3249,28 @@
         <v>38.95</v>
       </c>
       <c r="M24">
-        <v>5.9108808</v>
+        <v>6.179557200000001</v>
       </c>
       <c r="N24">
-        <v>33.0391192</v>
+        <v>32.7704428</v>
       </c>
       <c r="O24">
-        <v>4.95586788</v>
+        <v>4.91556642</v>
       </c>
       <c r="P24">
-        <v>28.08325132</v>
+        <v>27.85487638</v>
       </c>
       <c r="Q24">
-        <v>30.63325132</v>
+        <v>30.40487638</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08411942636942826</v>
+        <v>0.08455686861837081</v>
       </c>
       <c r="T24">
-        <v>0.7018337511827678</v>
+        <v>0.7098456595955231</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.589542458714444</v>
+        <v>6.303040612683382</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07572443883614553</v>
+        <v>0.07588562510413703</v>
       </c>
       <c r="C25">
-        <v>404.4053236002668</v>
+        <v>396.9420601641363</v>
       </c>
       <c r="D25">
-        <v>492.4093236002668</v>
+        <v>489.8940601641364</v>
       </c>
       <c r="E25">
-        <v>-287.696</v>
+        <v>-282.748</v>
       </c>
       <c r="F25">
-        <v>113.804</v>
+        <v>118.752</v>
       </c>
       <c r="G25">
         <v>25.8</v>
@@ -3331,45 +3331,45 @@
         <v>38.95</v>
       </c>
       <c r="M25">
-        <v>6.179557200000001</v>
+        <v>6.566985600000001</v>
       </c>
       <c r="N25">
-        <v>32.7704428</v>
+        <v>32.3830144</v>
       </c>
       <c r="O25">
-        <v>4.91556642</v>
+        <v>4.85745216</v>
       </c>
       <c r="P25">
-        <v>27.85487638</v>
+        <v>27.52556224</v>
       </c>
       <c r="Q25">
-        <v>30.40487638</v>
+        <v>30.07556224</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08455686861837081</v>
+        <v>0.08500582250544345</v>
       </c>
       <c r="T25">
-        <v>0.7098456595955231</v>
+        <v>0.718068407703351</v>
       </c>
       <c r="U25">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V25">
         <v>0.15</v>
       </c>
       <c r="W25">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y25">
-        <v>6.303040612683382</v>
+        <v>5.931184012341979</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07588562510413703</v>
+        <v>0.07585131137212851</v>
       </c>
       <c r="C26">
-        <v>396.9420601641363</v>
+        <v>392.5273604496206</v>
       </c>
       <c r="D26">
-        <v>489.8940601641364</v>
+        <v>490.4273604496206</v>
       </c>
       <c r="E26">
-        <v>-282.748</v>
+        <v>-277.8</v>
       </c>
       <c r="F26">
-        <v>118.752</v>
+        <v>123.7</v>
       </c>
       <c r="G26">
         <v>25.8</v>
@@ -3413,28 +3413,28 @@
         <v>38.95</v>
       </c>
       <c r="M26">
-        <v>6.5669856</v>
+        <v>6.840610000000001</v>
       </c>
       <c r="N26">
-        <v>32.3830144</v>
+        <v>32.10939</v>
       </c>
       <c r="O26">
-        <v>4.85745216</v>
+        <v>4.816408500000001</v>
       </c>
       <c r="P26">
-        <v>27.52556224</v>
+        <v>27.2929815</v>
       </c>
       <c r="Q26">
-        <v>30.07556224</v>
+        <v>29.8429815</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08500582250544345</v>
+        <v>0.08546674849617134</v>
       </c>
       <c r="T26">
-        <v>0.718068407703351</v>
+        <v>0.7265104290940543</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.93118401234198</v>
+        <v>5.693936651848301</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07585131137212851</v>
+        <v>0.07581699764012</v>
       </c>
       <c r="C27">
-        <v>392.5273604496206</v>
+        <v>388.1138231053553</v>
       </c>
       <c r="D27">
-        <v>490.4273604496206</v>
+        <v>490.9618231053554</v>
       </c>
       <c r="E27">
-        <v>-277.8</v>
+        <v>-272.852</v>
       </c>
       <c r="F27">
-        <v>123.7</v>
+        <v>128.648</v>
       </c>
       <c r="G27">
         <v>25.8</v>
@@ -3495,28 +3495,28 @@
         <v>38.95</v>
       </c>
       <c r="M27">
-        <v>6.840610000000001</v>
+        <v>7.1142344</v>
       </c>
       <c r="N27">
-        <v>32.10939</v>
+        <v>31.8357656</v>
       </c>
       <c r="O27">
-        <v>4.816408500000001</v>
+        <v>4.77536484</v>
       </c>
       <c r="P27">
-        <v>27.2929815</v>
+        <v>27.06040076</v>
       </c>
       <c r="Q27">
-        <v>29.8429815</v>
+        <v>29.61040076</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08546674849617134</v>
+        <v>0.0859401319461081</v>
       </c>
       <c r="T27">
-        <v>0.7265104290940543</v>
+        <v>0.7351806132250469</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.693936651848301</v>
+        <v>5.474939088315674</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07581699764012</v>
+        <v>0.07578268390811149</v>
       </c>
       <c r="C28">
-        <v>388.1138231053553</v>
+        <v>383.7014519357034</v>
       </c>
       <c r="D28">
-        <v>490.9618231053554</v>
+        <v>491.4974519357034</v>
       </c>
       <c r="E28">
-        <v>-272.852</v>
+        <v>-267.904</v>
       </c>
       <c r="F28">
-        <v>128.648</v>
+        <v>133.596</v>
       </c>
       <c r="G28">
         <v>25.8</v>
@@ -3577,28 +3577,28 @@
         <v>38.95</v>
       </c>
       <c r="M28">
-        <v>7.1142344</v>
+        <v>7.3878588</v>
       </c>
       <c r="N28">
-        <v>31.8357656</v>
+        <v>31.5621412</v>
       </c>
       <c r="O28">
-        <v>4.77536484</v>
+        <v>4.73432118</v>
       </c>
       <c r="P28">
-        <v>27.06040076</v>
+        <v>26.82782002</v>
       </c>
       <c r="Q28">
-        <v>29.61040076</v>
+        <v>29.37782002000001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.0859401319461081</v>
+        <v>0.08642648480563217</v>
       </c>
       <c r="T28">
-        <v>0.7351806132250469</v>
+        <v>0.7440883366472997</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.474939088315674</v>
+        <v>5.272163566526205</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07578268390811149</v>
+        <v>0.07574837017610297</v>
       </c>
       <c r="C29">
-        <v>383.7014519357034</v>
+        <v>379.2902507616484</v>
       </c>
       <c r="D29">
-        <v>491.4974519357034</v>
+        <v>492.0342507616484</v>
       </c>
       <c r="E29">
-        <v>-267.904</v>
+        <v>-262.956</v>
       </c>
       <c r="F29">
-        <v>133.596</v>
+        <v>138.544</v>
       </c>
       <c r="G29">
         <v>25.8</v>
@@ -3659,28 +3659,28 @@
         <v>38.95</v>
       </c>
       <c r="M29">
-        <v>7.3878588</v>
+        <v>7.661483200000001</v>
       </c>
       <c r="N29">
-        <v>31.5621412</v>
+        <v>31.2885168</v>
       </c>
       <c r="O29">
-        <v>4.73432118</v>
+        <v>4.693277520000001</v>
       </c>
       <c r="P29">
-        <v>26.82782002</v>
+        <v>26.59523928</v>
       </c>
       <c r="Q29">
-        <v>29.37782002000001</v>
+        <v>29.14523928</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08642648480563217</v>
+        <v>0.08692634746680969</v>
       </c>
       <c r="T29">
-        <v>0.7440883366472997</v>
+        <v>0.7532434968312816</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.272163566526205</v>
+        <v>5.08387201057884</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07574837017610297</v>
+        <v>0.07571405644409446</v>
       </c>
       <c r="C30">
-        <v>379.2902507616484</v>
+        <v>374.8802234208841</v>
       </c>
       <c r="D30">
-        <v>492.0342507616484</v>
+        <v>492.5722234208841</v>
       </c>
       <c r="E30">
-        <v>-262.956</v>
+        <v>-258.008</v>
       </c>
       <c r="F30">
-        <v>138.544</v>
+        <v>143.492</v>
       </c>
       <c r="G30">
         <v>25.8</v>
@@ -3741,28 +3741,28 @@
         <v>38.95</v>
       </c>
       <c r="M30">
-        <v>7.661483200000001</v>
+        <v>7.935107600000001</v>
       </c>
       <c r="N30">
-        <v>31.2885168</v>
+        <v>31.0148924</v>
       </c>
       <c r="O30">
-        <v>4.693277520000001</v>
+        <v>4.65223386</v>
       </c>
       <c r="P30">
-        <v>26.59523928</v>
+        <v>26.36265854</v>
       </c>
       <c r="Q30">
-        <v>29.14523928</v>
+        <v>28.91265854</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08692634746680969</v>
+        <v>0.08744029076633023</v>
       </c>
       <c r="T30">
-        <v>0.7532434968312816</v>
+        <v>0.762656548851432</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.08387201057884</v>
+        <v>4.908566079179568</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07571405644409446</v>
+        <v>0.07567974271208594</v>
       </c>
       <c r="C31">
-        <v>374.8802234208841</v>
+        <v>370.471373767907</v>
       </c>
       <c r="D31">
-        <v>492.5722234208841</v>
+        <v>493.111373767907</v>
       </c>
       <c r="E31">
-        <v>-258.008</v>
+        <v>-253.06</v>
       </c>
       <c r="F31">
-        <v>143.492</v>
+        <v>148.44</v>
       </c>
       <c r="G31">
         <v>25.8</v>
@@ -3823,28 +3823,28 @@
         <v>38.95</v>
       </c>
       <c r="M31">
-        <v>7.935107599999999</v>
+        <v>8.208731999999999</v>
       </c>
       <c r="N31">
-        <v>31.0148924</v>
+        <v>30.74126800000001</v>
       </c>
       <c r="O31">
-        <v>4.652233860000001</v>
+        <v>4.6111902</v>
       </c>
       <c r="P31">
-        <v>26.36265854000001</v>
+        <v>26.13007780000001</v>
       </c>
       <c r="Q31">
-        <v>28.91265854000001</v>
+        <v>28.68007780000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08744029076633023</v>
+        <v>0.08796891816012278</v>
       </c>
       <c r="T31">
-        <v>0.762656548851432</v>
+        <v>0.7723385452150151</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.90856607917957</v>
+        <v>4.744947209873584</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07567974271208594</v>
+        <v>0.07564542898007744</v>
       </c>
       <c r="C32">
-        <v>370.471373767907</v>
+        <v>366.0637056741076</v>
       </c>
       <c r="D32">
-        <v>493.111373767907</v>
+        <v>493.6517056741077</v>
       </c>
       <c r="E32">
-        <v>-253.06</v>
+        <v>-248.112</v>
       </c>
       <c r="F32">
-        <v>148.44</v>
+        <v>153.388</v>
       </c>
       <c r="G32">
         <v>25.8</v>
@@ -3905,28 +3905,28 @@
         <v>38.95</v>
       </c>
       <c r="M32">
-        <v>8.208731999999999</v>
+        <v>8.4823564</v>
       </c>
       <c r="N32">
-        <v>30.74126800000001</v>
+        <v>30.4676436</v>
       </c>
       <c r="O32">
-        <v>4.6111902</v>
+        <v>4.570146540000001</v>
       </c>
       <c r="P32">
-        <v>26.13007780000001</v>
+        <v>25.89749706</v>
       </c>
       <c r="Q32">
-        <v>28.68007780000001</v>
+        <v>28.44749706</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08796891816012278</v>
+        <v>0.08851286808706875</v>
       </c>
       <c r="T32">
-        <v>0.7723385452150151</v>
+        <v>0.7823011791543545</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.744947209873584</v>
+        <v>4.591884396651855</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07564542898007744</v>
+        <v>0.07629111524806892</v>
       </c>
       <c r="C33">
-        <v>366.0637056741076</v>
+        <v>351.1426980906945</v>
       </c>
       <c r="D33">
-        <v>493.6517056741077</v>
+        <v>483.6786980906945</v>
       </c>
       <c r="E33">
-        <v>-248.112</v>
+        <v>-243.164</v>
       </c>
       <c r="F33">
-        <v>153.388</v>
+        <v>158.336</v>
       </c>
       <c r="G33">
         <v>25.8</v>
@@ -3987,45 +3987,45 @@
         <v>38.95</v>
       </c>
       <c r="M33">
-        <v>8.4823564</v>
+        <v>9.151820800000001</v>
       </c>
       <c r="N33">
-        <v>30.4676436</v>
+        <v>29.7981792</v>
       </c>
       <c r="O33">
-        <v>4.570146540000001</v>
+        <v>4.46972688</v>
       </c>
       <c r="P33">
-        <v>25.89749706</v>
+        <v>25.32845232</v>
       </c>
       <c r="Q33">
-        <v>28.44749706</v>
+        <v>27.87845232</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08851286808706875</v>
+        <v>0.08907281654127783</v>
       </c>
       <c r="T33">
-        <v>0.7823011791543545</v>
+        <v>0.7925568317389684</v>
       </c>
       <c r="U33">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V33">
         <v>0.15</v>
       </c>
       <c r="W33">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.591884396651855</v>
+        <v>4.255983683596602</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07629111524806892</v>
+        <v>0.0762780515160604</v>
       </c>
       <c r="C34">
-        <v>351.1426980906945</v>
+        <v>346.3924796206456</v>
       </c>
       <c r="D34">
-        <v>483.6786980906945</v>
+        <v>483.8764796206457</v>
       </c>
       <c r="E34">
-        <v>-243.164</v>
+        <v>-238.216</v>
       </c>
       <c r="F34">
-        <v>158.336</v>
+        <v>163.284</v>
       </c>
       <c r="G34">
         <v>25.8</v>
@@ -4069,28 +4069,28 @@
         <v>38.95</v>
       </c>
       <c r="M34">
-        <v>9.151820800000001</v>
+        <v>9.437815200000001</v>
       </c>
       <c r="N34">
-        <v>29.7981792</v>
+        <v>29.5121848</v>
       </c>
       <c r="O34">
-        <v>4.46972688</v>
+        <v>4.426827719999999</v>
       </c>
       <c r="P34">
-        <v>25.32845232</v>
+        <v>25.08535708</v>
       </c>
       <c r="Q34">
-        <v>27.87845232</v>
+        <v>27.63535708</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08907281654127783</v>
+        <v>0.08964947987471703</v>
       </c>
       <c r="T34">
-        <v>0.7925568317389684</v>
+        <v>0.8031186232067052</v>
       </c>
       <c r="U34">
         <v>0.0578</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.255983683596602</v>
+        <v>4.127014481063371</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.0762780515160604</v>
+        <v>0.0762649877840519</v>
       </c>
       <c r="C35">
-        <v>346.3924796206456</v>
+        <v>341.6424229668432</v>
       </c>
       <c r="D35">
-        <v>483.8764796206457</v>
+        <v>484.0744229668432</v>
       </c>
       <c r="E35">
-        <v>-238.216</v>
+        <v>-233.268</v>
       </c>
       <c r="F35">
-        <v>163.284</v>
+        <v>168.232</v>
       </c>
       <c r="G35">
         <v>25.8</v>
@@ -4151,28 +4151,28 @@
         <v>38.95</v>
       </c>
       <c r="M35">
-        <v>9.437815200000001</v>
+        <v>9.723809600000003</v>
       </c>
       <c r="N35">
-        <v>29.5121848</v>
+        <v>29.2261904</v>
       </c>
       <c r="O35">
-        <v>4.426827719999999</v>
+        <v>4.38392856</v>
       </c>
       <c r="P35">
-        <v>25.08535708</v>
+        <v>24.84226184</v>
       </c>
       <c r="Q35">
-        <v>27.63535708</v>
+        <v>27.39226184</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08964947987471703</v>
+        <v>0.09024361785462409</v>
       </c>
       <c r="T35">
-        <v>0.8031186232067052</v>
+        <v>0.8140004689613431</v>
       </c>
       <c r="U35">
         <v>0.0578</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.127014481063371</v>
+        <v>4.005631702208566</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0762649877840519</v>
+        <v>0.07729317405204339</v>
       </c>
       <c r="C36">
-        <v>341.6424229668432</v>
+        <v>321.5949907946429</v>
       </c>
       <c r="D36">
-        <v>484.0744229668432</v>
+        <v>468.9749907946429</v>
       </c>
       <c r="E36">
-        <v>-233.268</v>
+        <v>-228.32</v>
       </c>
       <c r="F36">
-        <v>168.232</v>
+        <v>173.18</v>
       </c>
       <c r="G36">
         <v>25.8</v>
@@ -4233,45 +4233,45 @@
         <v>38.95</v>
       </c>
       <c r="M36">
-        <v>9.723809600000003</v>
+        <v>10.615934</v>
       </c>
       <c r="N36">
-        <v>29.2261904</v>
+        <v>28.334066</v>
       </c>
       <c r="O36">
-        <v>4.38392856</v>
+        <v>4.2501099</v>
       </c>
       <c r="P36">
-        <v>24.84226184</v>
+        <v>24.0839561</v>
       </c>
       <c r="Q36">
-        <v>27.39226184</v>
+        <v>26.6339561</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09024361785462409</v>
+        <v>0.09085603700314368</v>
       </c>
       <c r="T36">
-        <v>0.8140004689613431</v>
+        <v>0.8252171407392007</v>
       </c>
       <c r="U36">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V36">
         <v>0.15</v>
       </c>
       <c r="W36">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y36">
-        <v>4.005631702208566</v>
+        <v>3.669013013833733</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07729317405204339</v>
+        <v>0.07730986032003487</v>
       </c>
       <c r="C37">
-        <v>321.5949907946429</v>
+        <v>316.4097082525371</v>
       </c>
       <c r="D37">
-        <v>468.9749907946429</v>
+        <v>468.7377082525372</v>
       </c>
       <c r="E37">
-        <v>-228.32</v>
+        <v>-223.372</v>
       </c>
       <c r="F37">
-        <v>173.18</v>
+        <v>178.128</v>
       </c>
       <c r="G37">
         <v>25.8</v>
@@ -4315,28 +4315,28 @@
         <v>38.95</v>
       </c>
       <c r="M37">
-        <v>10.615934</v>
+        <v>10.9192464</v>
       </c>
       <c r="N37">
-        <v>28.334066</v>
+        <v>28.0307536</v>
       </c>
       <c r="O37">
-        <v>4.2501099</v>
+        <v>4.204613040000001</v>
       </c>
       <c r="P37">
-        <v>24.0839561</v>
+        <v>23.82614056</v>
       </c>
       <c r="Q37">
-        <v>26.6339561</v>
+        <v>26.37614056</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09085603700314368</v>
+        <v>0.0914875942500545</v>
       </c>
       <c r="T37">
-        <v>0.8252171407392007</v>
+        <v>0.8367843335101163</v>
       </c>
       <c r="U37">
         <v>0.0613</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.669013013833733</v>
+        <v>3.567095985671685</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07730986032003487</v>
+        <v>0.07820714658802637</v>
       </c>
       <c r="C38">
-        <v>316.4097082525372</v>
+        <v>299.0463390210771</v>
       </c>
       <c r="D38">
-        <v>468.7377082525372</v>
+        <v>456.322339021077</v>
       </c>
       <c r="E38">
-        <v>-223.372</v>
+        <v>-218.424</v>
       </c>
       <c r="F38">
-        <v>178.128</v>
+        <v>183.076</v>
       </c>
       <c r="G38">
         <v>25.8</v>
@@ -4397,45 +4397,45 @@
         <v>38.95</v>
       </c>
       <c r="M38">
-        <v>10.9192464</v>
+        <v>11.7351716</v>
       </c>
       <c r="N38">
-        <v>28.0307536</v>
+        <v>27.2148284</v>
       </c>
       <c r="O38">
-        <v>4.204613040000001</v>
+        <v>4.08222426</v>
       </c>
       <c r="P38">
-        <v>23.82614056</v>
+        <v>23.13260414</v>
       </c>
       <c r="Q38">
-        <v>26.37614056</v>
+        <v>25.68260414</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09148759425005448</v>
+        <v>0.09213920093337519</v>
       </c>
       <c r="T38">
-        <v>0.8367843335101162</v>
+        <v>0.8487187387499497</v>
       </c>
       <c r="U38">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V38">
         <v>0.15</v>
       </c>
       <c r="W38">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y38">
-        <v>3.567095985671686</v>
+        <v>3.319082270599264</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07820714658802637</v>
+        <v>0.07824763285601785</v>
       </c>
       <c r="C39">
-        <v>299.0463390210771</v>
+        <v>293.5536363767898</v>
       </c>
       <c r="D39">
-        <v>456.322339021077</v>
+        <v>455.7776363767898</v>
       </c>
       <c r="E39">
-        <v>-218.424</v>
+        <v>-213.476</v>
       </c>
       <c r="F39">
-        <v>183.076</v>
+        <v>188.024</v>
       </c>
       <c r="G39">
         <v>25.8</v>
@@ -4479,28 +4479,28 @@
         <v>38.95</v>
       </c>
       <c r="M39">
-        <v>11.7351716</v>
+        <v>12.0523384</v>
       </c>
       <c r="N39">
-        <v>27.2148284</v>
+        <v>26.8976616</v>
       </c>
       <c r="O39">
-        <v>4.08222426</v>
+        <v>4.03464924</v>
       </c>
       <c r="P39">
-        <v>23.13260414</v>
+        <v>22.86301236</v>
       </c>
       <c r="Q39">
-        <v>25.68260414</v>
+        <v>25.41301236</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09213920093337519</v>
+        <v>0.09281182718712556</v>
       </c>
       <c r="T39">
-        <v>0.8487187387499497</v>
+        <v>0.8610381248039715</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.319082270599264</v>
+        <v>3.231738000320336</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07824763285601785</v>
+        <v>0.07828811912400933</v>
       </c>
       <c r="C40">
-        <v>293.5536363767898</v>
+        <v>288.0622325829058</v>
       </c>
       <c r="D40">
-        <v>455.7776363767898</v>
+        <v>455.2342325829059</v>
       </c>
       <c r="E40">
-        <v>-213.476</v>
+        <v>-208.528</v>
       </c>
       <c r="F40">
-        <v>188.024</v>
+        <v>192.972</v>
       </c>
       <c r="G40">
         <v>25.8</v>
@@ -4561,28 +4561,28 @@
         <v>38.95</v>
       </c>
       <c r="M40">
-        <v>12.0523384</v>
+        <v>12.3695052</v>
       </c>
       <c r="N40">
-        <v>26.8976616</v>
+        <v>26.5804948</v>
       </c>
       <c r="O40">
-        <v>4.03464924</v>
+        <v>3.98707422</v>
       </c>
       <c r="P40">
-        <v>22.86301236</v>
+        <v>22.59342058</v>
       </c>
       <c r="Q40">
-        <v>25.41301236</v>
+        <v>25.14342058</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09281182718712556</v>
+        <v>0.09350650676067104</v>
       </c>
       <c r="T40">
-        <v>0.8610381248039715</v>
+        <v>0.8737614251548462</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.231738000320336</v>
+        <v>3.148872923389046</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07828811912400933</v>
+        <v>0.07832860539200082</v>
       </c>
       <c r="C41">
-        <v>288.0622325829058</v>
+        <v>282.5721229992697</v>
       </c>
       <c r="D41">
-        <v>455.2342325829059</v>
+        <v>454.6921229992697</v>
       </c>
       <c r="E41">
-        <v>-208.528</v>
+        <v>-203.58</v>
       </c>
       <c r="F41">
-        <v>192.972</v>
+        <v>197.92</v>
       </c>
       <c r="G41">
         <v>25.8</v>
@@ -4643,28 +4643,28 @@
         <v>38.95</v>
       </c>
       <c r="M41">
-        <v>12.3695052</v>
+        <v>12.686672</v>
       </c>
       <c r="N41">
-        <v>26.5804948</v>
+        <v>26.263328</v>
       </c>
       <c r="O41">
-        <v>3.98707422</v>
+        <v>3.9394992</v>
       </c>
       <c r="P41">
-        <v>22.59342058</v>
+        <v>22.3238288</v>
       </c>
       <c r="Q41">
-        <v>25.14342058</v>
+        <v>24.8738288</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09350650676067104</v>
+        <v>0.09422434232000138</v>
       </c>
       <c r="T41">
-        <v>0.8737614251548462</v>
+        <v>0.8869088355174172</v>
       </c>
       <c r="U41">
         <v>0.0641</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.148872923389046</v>
+        <v>3.070151100304319</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07832860539200082</v>
+        <v>0.08108739165999232</v>
       </c>
       <c r="C42">
-        <v>282.5721229992697</v>
+        <v>243.4972956696065</v>
       </c>
       <c r="D42">
-        <v>454.6921229992697</v>
+        <v>420.5652956696065</v>
       </c>
       <c r="E42">
-        <v>-203.58</v>
+        <v>-198.632</v>
       </c>
       <c r="F42">
-        <v>197.92</v>
+        <v>202.868</v>
       </c>
       <c r="G42">
         <v>25.8</v>
@@ -4725,45 +4725,45 @@
         <v>38.95</v>
       </c>
       <c r="M42">
-        <v>12.686672</v>
+        <v>14.5862092</v>
       </c>
       <c r="N42">
-        <v>26.263328</v>
+        <v>24.3637908</v>
       </c>
       <c r="O42">
-        <v>3.9394992</v>
+        <v>3.65456862</v>
       </c>
       <c r="P42">
-        <v>22.3238288</v>
+        <v>20.70922218</v>
       </c>
       <c r="Q42">
-        <v>24.8738288</v>
+        <v>23.25922218</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09422434232000138</v>
+        <v>0.09496651128812257</v>
       </c>
       <c r="T42">
-        <v>0.8869088355174172</v>
+        <v>0.9005019208075326</v>
       </c>
       <c r="U42">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V42">
         <v>0.15</v>
       </c>
       <c r="W42">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>3.070151100304319</v>
+        <v>2.670330547569549</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08108739165999232</v>
+        <v>0.08119417792798381</v>
       </c>
       <c r="C43">
-        <v>243.4972956696065</v>
+        <v>237.3310092929653</v>
       </c>
       <c r="D43">
-        <v>420.5652956696065</v>
+        <v>419.3470092929653</v>
       </c>
       <c r="E43">
-        <v>-198.632</v>
+        <v>-193.684</v>
       </c>
       <c r="F43">
-        <v>202.868</v>
+        <v>207.816</v>
       </c>
       <c r="G43">
         <v>25.8</v>
@@ -4807,28 +4807,28 @@
         <v>38.95</v>
       </c>
       <c r="M43">
-        <v>14.5862092</v>
+        <v>14.9419704</v>
       </c>
       <c r="N43">
-        <v>24.3637908</v>
+        <v>24.0080296</v>
       </c>
       <c r="O43">
-        <v>3.65456862</v>
+        <v>3.60120444</v>
       </c>
       <c r="P43">
-        <v>20.70922218</v>
+        <v>20.40682516</v>
       </c>
       <c r="Q43">
-        <v>23.25922218</v>
+        <v>22.95682516</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09496651128812257</v>
+        <v>0.09573427228962725</v>
       </c>
       <c r="T43">
-        <v>0.9005019208075326</v>
+        <v>0.9145637331766175</v>
       </c>
       <c r="U43">
         <v>0.07190000000000001</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.670330547569549</v>
+        <v>2.606751248817893</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08119417792798381</v>
+        <v>0.08130096419597529</v>
       </c>
       <c r="C44">
-        <v>237.3310092929653</v>
+        <v>231.1717607516439</v>
       </c>
       <c r="D44">
-        <v>419.3470092929653</v>
+        <v>418.1357607516439</v>
       </c>
       <c r="E44">
-        <v>-193.684</v>
+        <v>-188.736</v>
       </c>
       <c r="F44">
-        <v>207.816</v>
+        <v>212.764</v>
       </c>
       <c r="G44">
         <v>25.8</v>
@@ -4889,28 +4889,28 @@
         <v>38.95</v>
       </c>
       <c r="M44">
-        <v>14.9419704</v>
+        <v>15.2977316</v>
       </c>
       <c r="N44">
-        <v>24.0080296</v>
+        <v>23.6522684</v>
       </c>
       <c r="O44">
-        <v>3.60120444</v>
+        <v>3.54784026</v>
       </c>
       <c r="P44">
-        <v>20.40682516</v>
+        <v>20.10442814</v>
       </c>
       <c r="Q44">
-        <v>22.95682516</v>
+        <v>22.65442814</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09573427228962725</v>
+        <v>0.09652897227364085</v>
       </c>
       <c r="T44">
-        <v>0.9145637331766174</v>
+        <v>0.9291189424709334</v>
       </c>
       <c r="U44">
         <v>0.07190000000000001</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.606751248817893</v>
+        <v>2.546129126752361</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08130096419597529</v>
+        <v>0.08286635046396679</v>
       </c>
       <c r="C45">
-        <v>231.1717607516439</v>
+        <v>209.2384644553557</v>
       </c>
       <c r="D45">
-        <v>418.1357607516439</v>
+        <v>401.1504644553557</v>
       </c>
       <c r="E45">
-        <v>-188.736</v>
+        <v>-183.788</v>
       </c>
       <c r="F45">
-        <v>212.764</v>
+        <v>217.712</v>
       </c>
       <c r="G45">
         <v>25.8</v>
@@ -4971,45 +4971,45 @@
         <v>38.95</v>
       </c>
       <c r="M45">
-        <v>15.2977316</v>
+        <v>16.5025696</v>
       </c>
       <c r="N45">
-        <v>23.6522684</v>
+        <v>22.4474304</v>
       </c>
       <c r="O45">
-        <v>3.54784026</v>
+        <v>3.36711456</v>
       </c>
       <c r="P45">
-        <v>20.10442814</v>
+        <v>19.08031584</v>
       </c>
       <c r="Q45">
-        <v>22.65442814</v>
+        <v>21.63031584</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09652897227364085</v>
+        <v>0.09735205439994067</v>
       </c>
       <c r="T45">
-        <v>0.9291189424709334</v>
+        <v>0.9441939806686179</v>
       </c>
       <c r="U45">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V45">
         <v>0.15</v>
       </c>
       <c r="W45">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.546129126752361</v>
+        <v>2.360238492798115</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08286635046396679</v>
+        <v>0.08300628673195827</v>
       </c>
       <c r="C46">
-        <v>209.2384644553557</v>
+        <v>202.8390291714997</v>
       </c>
       <c r="D46">
-        <v>401.1504644553557</v>
+        <v>399.6990291714997</v>
       </c>
       <c r="E46">
-        <v>-183.788</v>
+        <v>-178.84</v>
       </c>
       <c r="F46">
-        <v>217.712</v>
+        <v>222.66</v>
       </c>
       <c r="G46">
         <v>25.8</v>
@@ -5053,28 +5053,28 @@
         <v>38.95</v>
       </c>
       <c r="M46">
-        <v>16.5025696</v>
+        <v>16.877628</v>
       </c>
       <c r="N46">
-        <v>22.4474304</v>
+        <v>22.072372</v>
       </c>
       <c r="O46">
-        <v>3.36711456</v>
+        <v>3.3108558</v>
       </c>
       <c r="P46">
-        <v>19.08031584</v>
+        <v>18.7615162</v>
       </c>
       <c r="Q46">
-        <v>21.63031584</v>
+        <v>21.3115162</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09735205439994067</v>
+        <v>0.09820506678537866</v>
       </c>
       <c r="T46">
-        <v>0.9441939806686179</v>
+        <v>0.9598172020734909</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.360238492798115</v>
+        <v>2.307788748513713</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08300628673195827</v>
+        <v>0.08314622299994975</v>
       </c>
       <c r="C47">
-        <v>202.8390291714997</v>
+        <v>196.450059135744</v>
       </c>
       <c r="D47">
-        <v>399.6990291714997</v>
+        <v>398.258059135744</v>
       </c>
       <c r="E47">
-        <v>-178.84</v>
+        <v>-173.892</v>
       </c>
       <c r="F47">
-        <v>222.66</v>
+        <v>227.608</v>
       </c>
       <c r="G47">
         <v>25.8</v>
@@ -5135,28 +5135,28 @@
         <v>38.95</v>
       </c>
       <c r="M47">
-        <v>16.877628</v>
+        <v>17.2526864</v>
       </c>
       <c r="N47">
-        <v>22.072372</v>
+        <v>21.6973136</v>
       </c>
       <c r="O47">
-        <v>3.3108558</v>
+        <v>3.25459704</v>
       </c>
       <c r="P47">
-        <v>18.7615162</v>
+        <v>18.44271656</v>
       </c>
       <c r="Q47">
-        <v>21.3115162</v>
+        <v>20.99271656</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09820506678537866</v>
+        <v>0.09908967222212917</v>
       </c>
       <c r="T47">
-        <v>0.9598172020734909</v>
+        <v>0.9760190613081741</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.307788748513713</v>
+        <v>2.257619427893849</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08314622299994975</v>
+        <v>0.08328615926794125</v>
       </c>
       <c r="C48">
-        <v>196.450059135744</v>
+        <v>190.0714415686927</v>
       </c>
       <c r="D48">
-        <v>398.258059135744</v>
+        <v>396.8274415686927</v>
       </c>
       <c r="E48">
-        <v>-173.892</v>
+        <v>-168.944</v>
       </c>
       <c r="F48">
-        <v>227.608</v>
+        <v>232.556</v>
       </c>
       <c r="G48">
         <v>25.8</v>
@@ -5217,28 +5217,28 @@
         <v>38.95</v>
       </c>
       <c r="M48">
-        <v>17.2526864</v>
+        <v>17.6277448</v>
       </c>
       <c r="N48">
-        <v>21.6973136</v>
+        <v>21.3222552</v>
       </c>
       <c r="O48">
-        <v>3.25459704</v>
+        <v>3.19833828</v>
       </c>
       <c r="P48">
-        <v>18.44271656</v>
+        <v>18.12391692</v>
       </c>
       <c r="Q48">
-        <v>20.99271656</v>
+        <v>20.67391692</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09908967222212917</v>
+        <v>0.1000076589961156</v>
       </c>
       <c r="T48">
-        <v>0.9760190613081741</v>
+        <v>0.9928323114573735</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.257619427893849</v>
+        <v>2.209584971981214</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08328615926794125</v>
+        <v>0.08342609553593273</v>
       </c>
       <c r="C49">
-        <v>190.0714415686927</v>
+        <v>183.7030653056486</v>
       </c>
       <c r="D49">
-        <v>396.8274415686927</v>
+        <v>395.4070653056486</v>
       </c>
       <c r="E49">
-        <v>-168.944</v>
+        <v>-163.996</v>
       </c>
       <c r="F49">
-        <v>232.556</v>
+        <v>237.504</v>
       </c>
       <c r="G49">
         <v>25.8</v>
@@ -5299,28 +5299,28 @@
         <v>38.95</v>
       </c>
       <c r="M49">
-        <v>17.6277448</v>
+        <v>18.0028032</v>
       </c>
       <c r="N49">
-        <v>21.3222552</v>
+        <v>20.9471968</v>
       </c>
       <c r="O49">
-        <v>3.19833828</v>
+        <v>3.14207952</v>
       </c>
       <c r="P49">
-        <v>18.12391692</v>
+        <v>17.80511728</v>
       </c>
       <c r="Q49">
-        <v>20.67391692</v>
+        <v>20.35511728</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1000076589961156</v>
+        <v>0.1009609529537168</v>
       </c>
       <c r="T49">
-        <v>0.9928323114573735</v>
+        <v>1.01029222507385</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.209584971981214</v>
+        <v>2.163551951731606</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08342609553593273</v>
+        <v>0.08356603180392422</v>
       </c>
       <c r="C50">
-        <v>183.7030653056486</v>
+        <v>177.3448207678182</v>
       </c>
       <c r="D50">
-        <v>395.4070653056486</v>
+        <v>393.9968207678182</v>
       </c>
       <c r="E50">
-        <v>-163.996</v>
+        <v>-159.048</v>
       </c>
       <c r="F50">
-        <v>237.504</v>
+        <v>242.452</v>
       </c>
       <c r="G50">
         <v>25.8</v>
@@ -5381,28 +5381,28 @@
         <v>38.95</v>
       </c>
       <c r="M50">
-        <v>18.0028032</v>
+        <v>18.3778616</v>
       </c>
       <c r="N50">
-        <v>20.9471968</v>
+        <v>20.5721384</v>
       </c>
       <c r="O50">
-        <v>3.14207952</v>
+        <v>3.08582076</v>
       </c>
       <c r="P50">
-        <v>17.80511728</v>
+        <v>17.48631764</v>
       </c>
       <c r="Q50">
-        <v>20.35511728</v>
+        <v>20.03631764</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1009609529537168</v>
+        <v>0.1019516309880867</v>
       </c>
       <c r="T50">
-        <v>1.01029222507385</v>
+        <v>1.02843684118509</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.163551951731606</v>
+        <v>2.119397830267696</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08356603180392422</v>
+        <v>0.08370596807191572</v>
       </c>
       <c r="C51">
-        <v>177.3448207678182</v>
+        <v>170.9965999341314</v>
       </c>
       <c r="D51">
-        <v>393.9968207678182</v>
+        <v>392.5965999341313</v>
       </c>
       <c r="E51">
-        <v>-159.048</v>
+        <v>-154.1</v>
       </c>
       <c r="F51">
-        <v>242.452</v>
+        <v>247.4</v>
       </c>
       <c r="G51">
         <v>25.8</v>
@@ -5463,28 +5463,28 @@
         <v>38.95</v>
       </c>
       <c r="M51">
-        <v>18.3778616</v>
+        <v>18.75292</v>
       </c>
       <c r="N51">
-        <v>20.5721384</v>
+        <v>20.19708</v>
       </c>
       <c r="O51">
-        <v>3.08582076</v>
+        <v>3.029562</v>
       </c>
       <c r="P51">
-        <v>17.48631764</v>
+        <v>17.167518</v>
       </c>
       <c r="Q51">
-        <v>20.03631764</v>
+        <v>19.717518</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1019516309880867</v>
+        <v>0.1029819361438314</v>
       </c>
       <c r="T51">
-        <v>1.02843684118509</v>
+        <v>1.04730724194078</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.119397830267696</v>
+        <v>2.077009873662341</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08370596807191572</v>
+        <v>0.08384590433990718</v>
       </c>
       <c r="C52">
-        <v>170.9965999341314</v>
+        <v>164.6582963136598</v>
       </c>
       <c r="D52">
-        <v>392.5965999341313</v>
+        <v>391.2062963136598</v>
       </c>
       <c r="E52">
-        <v>-154.1</v>
+        <v>-149.152</v>
       </c>
       <c r="F52">
-        <v>247.4</v>
+        <v>252.348</v>
       </c>
       <c r="G52">
         <v>25.8</v>
@@ -5545,28 +5545,28 @@
         <v>38.95</v>
       </c>
       <c r="M52">
-        <v>18.75292</v>
+        <v>19.1279784</v>
       </c>
       <c r="N52">
-        <v>20.19708</v>
+        <v>19.8220216</v>
       </c>
       <c r="O52">
-        <v>3.029562</v>
+        <v>2.97330324</v>
       </c>
       <c r="P52">
-        <v>17.167518</v>
+        <v>16.84871836</v>
       </c>
       <c r="Q52">
-        <v>19.717518</v>
+        <v>19.39871836</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1029819361438314</v>
+        <v>0.1040542945712392</v>
       </c>
       <c r="T52">
-        <v>1.04730724194078</v>
+        <v>1.066947863135477</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.077009873662341</v>
+        <v>2.03628418986504</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08384590433990718</v>
+        <v>0.09026224060789868</v>
       </c>
       <c r="C53">
-        <v>164.6582963136598</v>
+        <v>105.0616492858551</v>
       </c>
       <c r="D53">
-        <v>391.2062963136598</v>
+        <v>336.5576492858551</v>
       </c>
       <c r="E53">
-        <v>-149.152</v>
+        <v>-144.204</v>
       </c>
       <c r="F53">
-        <v>252.348</v>
+        <v>257.296</v>
       </c>
       <c r="G53">
         <v>25.8</v>
@@ -5627,45 +5627,45 @@
         <v>38.95</v>
       </c>
       <c r="M53">
-        <v>19.1279784</v>
+        <v>23.15664</v>
       </c>
       <c r="N53">
-        <v>19.8220216</v>
+        <v>15.79336</v>
       </c>
       <c r="O53">
-        <v>2.97330324</v>
+        <v>2.369004</v>
       </c>
       <c r="P53">
-        <v>16.84871836</v>
+        <v>13.424356</v>
       </c>
       <c r="Q53">
-        <v>19.39871836</v>
+        <v>15.974356</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1040542945712392</v>
+        <v>0.1051713345997889</v>
       </c>
       <c r="T53">
-        <v>1.066947863135477</v>
+        <v>1.08740684354662</v>
       </c>
       <c r="U53">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V53">
         <v>0.15</v>
       </c>
       <c r="W53">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y53">
-        <v>2.03628418986504</v>
+        <v>1.682022953243649</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09026224060789868</v>
+        <v>0.09052287687589017</v>
       </c>
       <c r="C54">
-        <v>105.0616492858551</v>
+        <v>98.21465624488593</v>
       </c>
       <c r="D54">
-        <v>336.5576492858551</v>
+        <v>334.6586562448859</v>
       </c>
       <c r="E54">
-        <v>-144.204</v>
+        <v>-139.256</v>
       </c>
       <c r="F54">
-        <v>257.296</v>
+        <v>262.244</v>
       </c>
       <c r="G54">
         <v>25.8</v>
@@ -5709,28 +5709,28 @@
         <v>38.95</v>
       </c>
       <c r="M54">
-        <v>23.15664</v>
+        <v>23.60196</v>
       </c>
       <c r="N54">
-        <v>15.79336</v>
+        <v>15.34804</v>
       </c>
       <c r="O54">
-        <v>2.369004</v>
+        <v>2.302206</v>
       </c>
       <c r="P54">
-        <v>13.424356</v>
+        <v>13.045834</v>
       </c>
       <c r="Q54">
-        <v>15.974356</v>
+        <v>15.595834</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1051713345997889</v>
+        <v>0.1063359082465748</v>
       </c>
       <c r="T54">
-        <v>1.08740684354662</v>
+        <v>1.108736418868876</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.682022953243649</v>
+        <v>1.650286671106976</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09052287687589017</v>
+        <v>0.09078351314388165</v>
       </c>
       <c r="C55">
-        <v>98.21465624488593</v>
+        <v>91.38897272554328</v>
       </c>
       <c r="D55">
-        <v>334.6586562448859</v>
+        <v>332.7809727255433</v>
       </c>
       <c r="E55">
-        <v>-139.256</v>
+        <v>-134.308</v>
       </c>
       <c r="F55">
-        <v>262.244</v>
+        <v>267.192</v>
       </c>
       <c r="G55">
         <v>25.8</v>
@@ -5791,28 +5791,28 @@
         <v>38.95</v>
       </c>
       <c r="M55">
-        <v>23.60196</v>
+        <v>24.04728</v>
       </c>
       <c r="N55">
-        <v>15.34804</v>
+        <v>14.90272</v>
       </c>
       <c r="O55">
-        <v>2.302206</v>
+        <v>2.235408</v>
       </c>
       <c r="P55">
-        <v>13.045834</v>
+        <v>12.667312</v>
       </c>
       <c r="Q55">
-        <v>15.595834</v>
+        <v>15.217312</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1063359082465748</v>
+        <v>0.1075511155301775</v>
       </c>
       <c r="T55">
-        <v>1.108736418868876</v>
+        <v>1.13099336703123</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.650286671106976</v>
+        <v>1.619725806827217</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09078351314388165</v>
+        <v>0.09104414941187314</v>
       </c>
       <c r="C56">
-        <v>91.38897272554328</v>
+        <v>84.58424204238634</v>
       </c>
       <c r="D56">
-        <v>332.7809727255433</v>
+        <v>330.9242420423864</v>
       </c>
       <c r="E56">
-        <v>-134.308</v>
+        <v>-129.36</v>
       </c>
       <c r="F56">
-        <v>267.192</v>
+        <v>272.14</v>
       </c>
       <c r="G56">
         <v>25.8</v>
@@ -5873,28 +5873,28 @@
         <v>38.95</v>
       </c>
       <c r="M56">
-        <v>24.04728</v>
+        <v>24.4926</v>
       </c>
       <c r="N56">
-        <v>14.90272</v>
+        <v>14.4574</v>
       </c>
       <c r="O56">
-        <v>2.235408</v>
+        <v>2.16861</v>
       </c>
       <c r="P56">
-        <v>12.667312</v>
+        <v>12.28879</v>
       </c>
       <c r="Q56">
-        <v>15.217312</v>
+        <v>14.83879</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1075511155301775</v>
+        <v>0.1088203320263848</v>
       </c>
       <c r="T56">
-        <v>1.13099336703123</v>
+        <v>1.154239512889688</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.619725806827217</v>
+        <v>1.590276246703086</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09104414941187314</v>
+        <v>0.09130478567986464</v>
       </c>
       <c r="C57">
-        <v>84.58424204238634</v>
+        <v>77.8001154262227</v>
       </c>
       <c r="D57">
-        <v>330.9242420423864</v>
+        <v>329.0881154262227</v>
       </c>
       <c r="E57">
-        <v>-129.36</v>
+        <v>-124.412</v>
       </c>
       <c r="F57">
-        <v>272.14</v>
+        <v>277.088</v>
       </c>
       <c r="G57">
         <v>25.8</v>
@@ -5955,28 +5955,28 @@
         <v>38.95</v>
       </c>
       <c r="M57">
-        <v>24.4926</v>
+        <v>24.93792</v>
       </c>
       <c r="N57">
-        <v>14.4574</v>
+        <v>14.01208</v>
       </c>
       <c r="O57">
-        <v>2.16861</v>
+        <v>2.101812</v>
       </c>
       <c r="P57">
-        <v>12.28879</v>
+        <v>11.910268</v>
       </c>
       <c r="Q57">
-        <v>14.83879</v>
+        <v>14.460268</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1088203320263848</v>
+        <v>0.1101472401815105</v>
       </c>
       <c r="T57">
-        <v>1.154239512889688</v>
+        <v>1.178542301741713</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.590276246703086</v>
+        <v>1.561878456583388</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09130478567986464</v>
+        <v>0.09156542194785613</v>
       </c>
       <c r="C58">
-        <v>77.8001154262227</v>
+        <v>71.03625180570469</v>
       </c>
       <c r="D58">
-        <v>329.0881154262227</v>
+        <v>327.2722518057047</v>
       </c>
       <c r="E58">
-        <v>-124.412</v>
+        <v>-119.4639999999999</v>
       </c>
       <c r="F58">
-        <v>277.088</v>
+        <v>282.0360000000001</v>
       </c>
       <c r="G58">
         <v>25.8</v>
@@ -6037,28 +6037,28 @@
         <v>38.95</v>
       </c>
       <c r="M58">
-        <v>24.93792</v>
+        <v>25.38324</v>
       </c>
       <c r="N58">
-        <v>14.01208</v>
+        <v>13.56676</v>
       </c>
       <c r="O58">
-        <v>2.101812</v>
+        <v>2.035014</v>
       </c>
       <c r="P58">
-        <v>11.910268</v>
+        <v>11.531746</v>
       </c>
       <c r="Q58">
-        <v>14.460268</v>
+        <v>14.081746</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1101472401815105</v>
+        <v>0.1115358649950143</v>
       </c>
       <c r="T58">
-        <v>1.178542301741713</v>
+        <v>1.203975452865925</v>
       </c>
       <c r="U58">
         <v>0.09</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.561878456583388</v>
+        <v>1.5344770801521</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09156542194785613</v>
+        <v>0.09182605821584761</v>
       </c>
       <c r="C59">
-        <v>71.03625180570469</v>
+        <v>64.29231759611645</v>
       </c>
       <c r="D59">
-        <v>327.2722518057047</v>
+        <v>325.4763175961165</v>
       </c>
       <c r="E59">
-        <v>-119.4639999999999</v>
+        <v>-114.516</v>
       </c>
       <c r="F59">
-        <v>282.0360000000001</v>
+        <v>286.984</v>
       </c>
       <c r="G59">
         <v>25.8</v>
@@ -6119,28 +6119,28 @@
         <v>38.95</v>
       </c>
       <c r="M59">
-        <v>25.38324</v>
+        <v>25.82856</v>
       </c>
       <c r="N59">
-        <v>13.56676</v>
+        <v>13.12144</v>
       </c>
       <c r="O59">
-        <v>2.035014</v>
+        <v>1.968216</v>
       </c>
       <c r="P59">
-        <v>11.531746</v>
+        <v>11.153224</v>
       </c>
       <c r="Q59">
-        <v>14.081746</v>
+        <v>13.703224</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1115358649950143</v>
+        <v>0.1129906147996372</v>
       </c>
       <c r="T59">
-        <v>1.203975452865925</v>
+        <v>1.230619706424623</v>
       </c>
       <c r="U59">
         <v>0.09</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.5344770801521</v>
+        <v>1.508020578770167</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09182605821584761</v>
+        <v>0.1220051876582675</v>
       </c>
       <c r="C60">
-        <v>64.2923175961165</v>
+        <v>-67.11365383265954</v>
       </c>
       <c r="D60">
-        <v>325.4763175961165</v>
+        <v>199.0183461673405</v>
       </c>
       <c r="E60">
-        <v>-114.516</v>
+        <v>-109.568</v>
       </c>
       <c r="F60">
-        <v>286.984</v>
+        <v>291.932</v>
       </c>
       <c r="G60">
         <v>25.8</v>
@@ -6201,45 +6201,45 @@
         <v>38.95</v>
       </c>
       <c r="M60">
-        <v>25.82856</v>
+        <v>42.85561760000001</v>
       </c>
       <c r="N60">
-        <v>13.12144000000001</v>
+        <v>-3.905617600000006</v>
       </c>
       <c r="O60">
-        <v>1.968216000000001</v>
+        <v>-0.585842640000001</v>
       </c>
       <c r="P60">
-        <v>11.15322400000001</v>
+        <v>-3.319774960000005</v>
       </c>
       <c r="Q60">
-        <v>13.70322400000001</v>
+        <v>-0.7697749600000057</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1129906147996372</v>
+        <v>0.1151243629025315</v>
       </c>
       <c r="T60">
-        <v>1.230619706424623</v>
+        <v>1.269700052270514</v>
       </c>
       <c r="U60">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.15</v>
+        <v>0.1363298518885421</v>
       </c>
       <c r="W60">
-        <v>0.0765</v>
+        <v>0.126786777742762</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y60">
-        <v>1.508020578770168</v>
+        <v>0.9088656792569475</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1220051876582675</v>
+        <v>0.1230151876582675</v>
       </c>
       <c r="C61">
-        <v>-67.11365383265954</v>
+        <v>-74.61625961648576</v>
       </c>
       <c r="D61">
-        <v>199.0183461673405</v>
+        <v>196.4637403835142</v>
       </c>
       <c r="E61">
-        <v>-109.568</v>
+        <v>-104.62</v>
       </c>
       <c r="F61">
-        <v>291.932</v>
+        <v>296.88</v>
       </c>
       <c r="G61">
         <v>25.8</v>
@@ -6283,37 +6283,37 @@
         <v>38.95</v>
       </c>
       <c r="M61">
-        <v>42.85561760000001</v>
+        <v>43.58198400000001</v>
       </c>
       <c r="N61">
-        <v>-3.905617600000006</v>
+        <v>-4.631984000000003</v>
       </c>
       <c r="O61">
-        <v>-0.585842640000001</v>
+        <v>-0.6947976000000003</v>
       </c>
       <c r="P61">
-        <v>-3.319774960000005</v>
+        <v>-3.937186400000003</v>
       </c>
       <c r="Q61">
-        <v>-0.7697749600000057</v>
+        <v>-1.387186400000003</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1151243629025315</v>
+        <v>0.1168574719750948</v>
       </c>
       <c r="T61">
-        <v>1.269700052270514</v>
+        <v>1.301442553577277</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.1363298518885421</v>
+        <v>0.1340576876903997</v>
       </c>
       <c r="W61">
-        <v>0.126786777742762</v>
+        <v>0.1271203314470493</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.9088656792569475</v>
+        <v>0.8937179179359984</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1230151876582675</v>
+        <v>0.1240251876582675</v>
       </c>
       <c r="C62">
-        <v>-74.61625961648576</v>
+        <v>-82.05411454314014</v>
       </c>
       <c r="D62">
-        <v>196.4637403835142</v>
+        <v>193.9738854568598</v>
       </c>
       <c r="E62">
-        <v>-104.62</v>
+        <v>-99.67200000000003</v>
       </c>
       <c r="F62">
-        <v>296.88</v>
+        <v>301.828</v>
       </c>
       <c r="G62">
         <v>25.8</v>
@@ -6365,37 +6365,37 @@
         <v>38.95</v>
       </c>
       <c r="M62">
-        <v>43.58198400000001</v>
+        <v>44.3083504</v>
       </c>
       <c r="N62">
-        <v>-4.631984000000003</v>
+        <v>-5.358350399999999</v>
       </c>
       <c r="O62">
-        <v>-0.6947976000000003</v>
+        <v>-0.8037525599999998</v>
       </c>
       <c r="P62">
-        <v>-3.937186400000003</v>
+        <v>-4.55459784</v>
       </c>
       <c r="Q62">
-        <v>-1.387186400000003</v>
+        <v>-2.00459784</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1168574719750948</v>
+        <v>0.1186794584359946</v>
       </c>
       <c r="T62">
-        <v>1.301442553577277</v>
+        <v>1.334812875463874</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.1340576876903997</v>
+        <v>0.1318600206790817</v>
       </c>
       <c r="W62">
-        <v>0.1271203314470493</v>
+        <v>0.1274429489643108</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8937179179359984</v>
+        <v>0.8790668045272116</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1240251876582675</v>
+        <v>0.1250351876582675</v>
       </c>
       <c r="C63">
-        <v>-82.05411454314014</v>
+        <v>-89.42964963540183</v>
       </c>
       <c r="D63">
-        <v>193.9738854568598</v>
+        <v>191.5463503645982</v>
       </c>
       <c r="E63">
-        <v>-99.67200000000003</v>
+        <v>-94.72399999999999</v>
       </c>
       <c r="F63">
-        <v>301.828</v>
+        <v>306.776</v>
       </c>
       <c r="G63">
         <v>25.8</v>
@@ -6447,37 +6447,37 @@
         <v>38.95</v>
       </c>
       <c r="M63">
-        <v>44.3083504</v>
+        <v>45.03471680000001</v>
       </c>
       <c r="N63">
-        <v>-5.358350399999999</v>
+        <v>-6.084716800000002</v>
       </c>
       <c r="O63">
-        <v>-0.8037525599999998</v>
+        <v>-0.9127075200000003</v>
       </c>
       <c r="P63">
-        <v>-4.55459784</v>
+        <v>-5.172009280000002</v>
       </c>
       <c r="Q63">
-        <v>-2.00459784</v>
+        <v>-2.622009280000002</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1186794584359946</v>
+        <v>0.1205973389211524</v>
       </c>
       <c r="T63">
-        <v>1.334812875463874</v>
+        <v>1.369939530081344</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.1318600206790817</v>
+        <v>0.1297332461519998</v>
       </c>
       <c r="W63">
-        <v>0.1274429489643108</v>
+        <v>0.1277551594648864</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8790668045272116</v>
+        <v>0.8648883076799985</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1250351876582675</v>
+        <v>0.1260451876582675</v>
       </c>
       <c r="C64">
-        <v>-89.42964963540183</v>
+        <v>-96.74517572561354</v>
       </c>
       <c r="D64">
-        <v>191.5463503645982</v>
+        <v>189.1788242743864</v>
       </c>
       <c r="E64">
-        <v>-94.72399999999999</v>
+        <v>-89.77600000000001</v>
       </c>
       <c r="F64">
-        <v>306.776</v>
+        <v>311.724</v>
       </c>
       <c r="G64">
         <v>25.8</v>
@@ -6529,37 +6529,37 @@
         <v>38.95</v>
       </c>
       <c r="M64">
-        <v>45.03471680000001</v>
+        <v>45.7610832</v>
       </c>
       <c r="N64">
-        <v>-6.084716800000002</v>
+        <v>-6.811083199999999</v>
       </c>
       <c r="O64">
-        <v>-0.9127075200000003</v>
+        <v>-1.02166248</v>
       </c>
       <c r="P64">
-        <v>-5.172009280000002</v>
+        <v>-5.789420719999999</v>
       </c>
       <c r="Q64">
-        <v>-2.622009280000002</v>
+        <v>-3.239420719999999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1205973389211524</v>
+        <v>0.1226188886217241</v>
       </c>
       <c r="T64">
-        <v>1.369939530081344</v>
+        <v>1.406964922786246</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.1297332461519998</v>
+        <v>0.1276739882765712</v>
       </c>
       <c r="W64">
-        <v>0.1277551594648864</v>
+        <v>0.1280574585209994</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8648883076799985</v>
+        <v>0.8511599218438082</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1260451876582675</v>
+        <v>0.1270551876582675</v>
       </c>
       <c r="C65">
-        <v>-96.74517572561354</v>
+        <v>-104.0028907928052</v>
       </c>
       <c r="D65">
-        <v>189.1788242743864</v>
+        <v>186.8691092071948</v>
       </c>
       <c r="E65">
-        <v>-89.77600000000001</v>
+        <v>-84.82799999999997</v>
       </c>
       <c r="F65">
-        <v>311.724</v>
+        <v>316.672</v>
       </c>
       <c r="G65">
         <v>25.8</v>
@@ -6611,37 +6611,37 @@
         <v>38.95</v>
       </c>
       <c r="M65">
-        <v>45.7610832</v>
+        <v>46.48744960000001</v>
       </c>
       <c r="N65">
-        <v>-6.811083199999999</v>
+        <v>-7.537449600000002</v>
       </c>
       <c r="O65">
-        <v>-1.02166248</v>
+        <v>-1.13061744</v>
       </c>
       <c r="P65">
-        <v>-5.789420719999999</v>
+        <v>-6.406832160000002</v>
       </c>
       <c r="Q65">
-        <v>-3.239420719999999</v>
+        <v>-3.856832160000002</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1226188886217241</v>
+        <v>0.1247527466389942</v>
       </c>
       <c r="T65">
-        <v>1.406964922786246</v>
+        <v>1.44604728175253</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.1276739882765712</v>
+        <v>0.1256790822097498</v>
       </c>
       <c r="W65">
-        <v>0.1280574585209994</v>
+        <v>0.1283503107316087</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8511599218438082</v>
+        <v>0.8378605480649985</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1270551876582675</v>
+        <v>0.1280651876582675</v>
       </c>
       <c r="C66">
-        <v>-104.0028907928052</v>
+        <v>-111.2048867688182</v>
       </c>
       <c r="D66">
-        <v>186.8691092071948</v>
+        <v>184.6151132311818</v>
       </c>
       <c r="E66">
-        <v>-84.82799999999997</v>
+        <v>-79.88</v>
       </c>
       <c r="F66">
-        <v>316.672</v>
+        <v>321.62</v>
       </c>
       <c r="G66">
         <v>25.8</v>
@@ -6693,37 +6693,37 @@
         <v>38.95</v>
       </c>
       <c r="M66">
-        <v>46.48744960000001</v>
+        <v>47.21381600000001</v>
       </c>
       <c r="N66">
-        <v>-7.537449600000002</v>
+        <v>-8.263816000000006</v>
       </c>
       <c r="O66">
-        <v>-1.13061744</v>
+        <v>-1.239572400000001</v>
       </c>
       <c r="P66">
-        <v>-6.406832160000002</v>
+        <v>-7.024243600000005</v>
       </c>
       <c r="Q66">
-        <v>-3.856832160000002</v>
+        <v>-4.474243600000005</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1247527466389942</v>
+        <v>0.1270085394001083</v>
       </c>
       <c r="T66">
-        <v>1.44604728175253</v>
+        <v>1.487362918374031</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.1256790822097498</v>
+        <v>0.1237455578680613</v>
       </c>
       <c r="W66">
-        <v>0.1283503107316087</v>
+        <v>0.1286341521049686</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8378605480649985</v>
+        <v>0.8249703857870755</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1280651876582675</v>
+        <v>0.1290751876582675</v>
       </c>
       <c r="C67">
-        <v>-111.2048867688182</v>
+        <v>-118.3531558577335</v>
       </c>
       <c r="D67">
-        <v>184.6151132311818</v>
+        <v>182.4148441422666</v>
       </c>
       <c r="E67">
-        <v>-79.88</v>
+        <v>-74.93199999999996</v>
       </c>
       <c r="F67">
-        <v>321.62</v>
+        <v>326.568</v>
       </c>
       <c r="G67">
         <v>25.8</v>
@@ -6775,37 +6775,37 @@
         <v>38.95</v>
       </c>
       <c r="M67">
-        <v>47.21381600000001</v>
+        <v>47.94018240000001</v>
       </c>
       <c r="N67">
-        <v>-8.263816000000006</v>
+        <v>-8.990182400000009</v>
       </c>
       <c r="O67">
-        <v>-1.239572400000001</v>
+        <v>-1.348527360000001</v>
       </c>
       <c r="P67">
-        <v>-7.024243600000005</v>
+        <v>-7.641655040000008</v>
       </c>
       <c r="Q67">
-        <v>-4.474243600000005</v>
+        <v>-5.091655040000008</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1270085394001083</v>
+        <v>0.1293970258530527</v>
       </c>
       <c r="T67">
-        <v>1.487362918374031</v>
+        <v>1.531108886561503</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.1237455578680613</v>
+        <v>0.1218706251730907</v>
       </c>
       <c r="W67">
-        <v>0.1286341521049686</v>
+        <v>0.1289093922245903</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8249703857870755</v>
+        <v>0.8124708344872712</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1290751876582675</v>
+        <v>0.1300851876582675</v>
       </c>
       <c r="C68">
-        <v>-118.3531558577335</v>
+        <v>-125.4495964087251</v>
       </c>
       <c r="D68">
-        <v>182.4148441422666</v>
+        <v>180.2664035912749</v>
       </c>
       <c r="E68">
-        <v>-74.93199999999996</v>
+        <v>-69.98399999999998</v>
       </c>
       <c r="F68">
-        <v>326.568</v>
+        <v>331.516</v>
       </c>
       <c r="G68">
         <v>25.8</v>
@@ -6857,37 +6857,37 @@
         <v>38.95</v>
       </c>
       <c r="M68">
-        <v>47.94018240000001</v>
+        <v>48.66654880000001</v>
       </c>
       <c r="N68">
-        <v>-8.990182400000009</v>
+        <v>-9.716548800000005</v>
       </c>
       <c r="O68">
-        <v>-1.348527360000001</v>
+        <v>-1.457482320000001</v>
       </c>
       <c r="P68">
-        <v>-7.641655040000008</v>
+        <v>-8.259066480000005</v>
       </c>
       <c r="Q68">
-        <v>-5.091655040000008</v>
+        <v>-5.709066480000005</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1293970258530527</v>
+        <v>0.1319302690607209</v>
       </c>
       <c r="T68">
-        <v>1.531108886561503</v>
+        <v>1.577506125548215</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.1218706251730907</v>
+        <v>0.1200516606182684</v>
       </c>
       <c r="W68">
-        <v>0.1289093922245903</v>
+        <v>0.1291764162212382</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8124708344872712</v>
+        <v>0.8003444041217896</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1300851876582675</v>
+        <v>0.1684837780847834</v>
       </c>
       <c r="C69">
-        <v>-125.4495964087251</v>
+        <v>-186.1510341298226</v>
       </c>
       <c r="D69">
-        <v>180.2664035912749</v>
+        <v>124.5129658701775</v>
       </c>
       <c r="E69">
-        <v>-69.98399999999998</v>
+        <v>-65.03599999999994</v>
       </c>
       <c r="F69">
-        <v>331.516</v>
+        <v>336.4640000000001</v>
       </c>
       <c r="G69">
         <v>25.8</v>
@@ -6939,45 +6939,45 @@
         <v>38.95</v>
       </c>
       <c r="M69">
-        <v>48.66654880000001</v>
+        <v>67.56197120000002</v>
       </c>
       <c r="N69">
-        <v>-9.716548800000005</v>
+        <v>-28.61197120000001</v>
       </c>
       <c r="O69">
-        <v>-1.457482320000001</v>
+        <v>-4.291795680000002</v>
       </c>
       <c r="P69">
-        <v>-8.259066480000005</v>
+        <v>-24.32017552000001</v>
       </c>
       <c r="Q69">
-        <v>-5.709066480000005</v>
+        <v>-21.77017552000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1319302690607209</v>
+        <v>0.1367111850517305</v>
       </c>
       <c r="T69">
-        <v>1.577506125548215</v>
+        <v>1.665070280911901</v>
       </c>
       <c r="U69">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1200516606182684</v>
+        <v>0.0864761624953891</v>
       </c>
       <c r="W69">
-        <v>0.1291764162212382</v>
+        <v>0.1834355865709259</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y69">
-        <v>0.8003444041217896</v>
+        <v>0.5765077499692608</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1684837780847834</v>
+        <v>0.1700337780847834</v>
       </c>
       <c r="C70">
-        <v>-186.1510341298226</v>
+        <v>-192.6343560164461</v>
       </c>
       <c r="D70">
-        <v>124.5129658701775</v>
+        <v>122.9776439835539</v>
       </c>
       <c r="E70">
-        <v>-65.03599999999994</v>
+        <v>-60.08799999999997</v>
       </c>
       <c r="F70">
-        <v>336.4640000000001</v>
+        <v>341.412</v>
       </c>
       <c r="G70">
         <v>25.8</v>
@@ -7021,37 +7021,37 @@
         <v>38.95</v>
       </c>
       <c r="M70">
-        <v>67.56197120000002</v>
+        <v>68.55552960000001</v>
       </c>
       <c r="N70">
-        <v>-28.61197120000001</v>
+        <v>-29.60552960000001</v>
       </c>
       <c r="O70">
-        <v>-4.291795680000002</v>
+        <v>-4.440829440000002</v>
       </c>
       <c r="P70">
-        <v>-24.32017552000001</v>
+        <v>-25.16470016000001</v>
       </c>
       <c r="Q70">
-        <v>-21.77017552000001</v>
+        <v>-22.61470016000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1367111850517305</v>
+        <v>0.139643803924367</v>
       </c>
       <c r="T70">
-        <v>1.665070280911901</v>
+        <v>1.718782225457446</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.0864761624953891</v>
+        <v>0.08522288477806463</v>
       </c>
       <c r="W70">
-        <v>0.1834355865709259</v>
+        <v>0.1836872447365646</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5765077499692608</v>
+        <v>0.5681525651870976</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1700337780847834</v>
+        <v>0.1715837780847834</v>
       </c>
       <c r="C71">
-        <v>-192.6343560164461</v>
+        <v>-199.0802761527168</v>
       </c>
       <c r="D71">
-        <v>122.9776439835539</v>
+        <v>121.4797238472832</v>
       </c>
       <c r="E71">
-        <v>-60.08799999999997</v>
+        <v>-55.13999999999999</v>
       </c>
       <c r="F71">
-        <v>341.412</v>
+        <v>346.36</v>
       </c>
       <c r="G71">
         <v>25.8</v>
@@ -7103,37 +7103,37 @@
         <v>38.95</v>
       </c>
       <c r="M71">
-        <v>68.55552960000001</v>
+        <v>69.54908800000001</v>
       </c>
       <c r="N71">
-        <v>-29.60552960000001</v>
+        <v>-30.59908800000001</v>
       </c>
       <c r="O71">
-        <v>-4.440829440000002</v>
+        <v>-4.589863200000001</v>
       </c>
       <c r="P71">
-        <v>-25.16470016000001</v>
+        <v>-26.00922480000001</v>
       </c>
       <c r="Q71">
-        <v>-22.61470016000001</v>
+        <v>-23.45922480000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.139643803924367</v>
+        <v>0.1427719307218459</v>
       </c>
       <c r="T71">
-        <v>1.718782225457446</v>
+        <v>1.776074966306027</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.08522288477806463</v>
+        <v>0.08400541499552085</v>
       </c>
       <c r="W71">
-        <v>0.1836872447365646</v>
+        <v>0.1839317126688994</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5681525651870976</v>
+        <v>0.560036099970139</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1715837780847834</v>
+        <v>0.1731337780847834</v>
       </c>
       <c r="C72">
-        <v>-199.0802761527168</v>
+        <v>-205.490144799677</v>
       </c>
       <c r="D72">
-        <v>121.4797238472832</v>
+        <v>120.0178552003231</v>
       </c>
       <c r="E72">
-        <v>-55.13999999999999</v>
+        <v>-50.19199999999995</v>
       </c>
       <c r="F72">
-        <v>346.36</v>
+        <v>351.308</v>
       </c>
       <c r="G72">
         <v>25.8</v>
@@ -7185,37 +7185,37 @@
         <v>38.95</v>
       </c>
       <c r="M72">
-        <v>69.54908800000001</v>
+        <v>70.54264640000001</v>
       </c>
       <c r="N72">
-        <v>-30.59908800000001</v>
+        <v>-31.59264640000001</v>
       </c>
       <c r="O72">
-        <v>-4.589863200000001</v>
+        <v>-4.738896960000001</v>
       </c>
       <c r="P72">
-        <v>-26.00922480000001</v>
+        <v>-26.85374944</v>
       </c>
       <c r="Q72">
-        <v>-23.45922480000001</v>
+        <v>-24.30374944</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1427719307218459</v>
+        <v>0.1461157904019096</v>
       </c>
       <c r="T72">
-        <v>1.776074966306027</v>
+        <v>1.837318930661408</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.08400541499552085</v>
+        <v>0.08282224013642901</v>
       </c>
       <c r="W72">
-        <v>0.1839317126688994</v>
+        <v>0.1841692941806051</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.560036099970139</v>
+        <v>0.5521482675761934</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1731337780847834</v>
+        <v>0.1746837780847833</v>
       </c>
       <c r="C73">
-        <v>-205.4901447996769</v>
+        <v>-211.865247995863</v>
       </c>
       <c r="D73">
-        <v>120.0178552003231</v>
+        <v>118.5907520041369</v>
       </c>
       <c r="E73">
-        <v>-50.19200000000001</v>
+        <v>-45.24400000000003</v>
       </c>
       <c r="F73">
-        <v>351.308</v>
+        <v>356.256</v>
       </c>
       <c r="G73">
         <v>25.8</v>
@@ -7267,37 +7267,37 @@
         <v>38.95</v>
       </c>
       <c r="M73">
-        <v>70.5426464</v>
+        <v>71.53620479999999</v>
       </c>
       <c r="N73">
-        <v>-31.59264639999999</v>
+        <v>-32.58620479999999</v>
       </c>
       <c r="O73">
-        <v>-4.738896959999999</v>
+        <v>-4.887930719999998</v>
       </c>
       <c r="P73">
-        <v>-26.85374943999999</v>
+        <v>-27.69827407999999</v>
       </c>
       <c r="Q73">
-        <v>-24.30374943999999</v>
+        <v>-25.14827407999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1461157904019095</v>
+        <v>0.1496984972019777</v>
       </c>
       <c r="T73">
-        <v>1.837318930661407</v>
+        <v>1.902937463899314</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.08282224013642903</v>
+        <v>0.0816719312456453</v>
       </c>
       <c r="W73">
-        <v>0.1841692941806051</v>
+        <v>0.1844002762058744</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5521482675761935</v>
+        <v>0.5444795416376353</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1746837780847833</v>
+        <v>0.1762337780847834</v>
       </c>
       <c r="C74">
-        <v>-211.865247995863</v>
+        <v>-218.2068113307087</v>
       </c>
       <c r="D74">
-        <v>118.5907520041369</v>
+        <v>117.1971886692913</v>
       </c>
       <c r="E74">
-        <v>-45.24400000000003</v>
+        <v>-40.29599999999999</v>
       </c>
       <c r="F74">
-        <v>356.256</v>
+        <v>361.204</v>
       </c>
       <c r="G74">
         <v>25.8</v>
@@ -7349,37 +7349,37 @@
         <v>38.95</v>
       </c>
       <c r="M74">
-        <v>71.53620479999999</v>
+        <v>72.5297632</v>
       </c>
       <c r="N74">
-        <v>-32.58620479999999</v>
+        <v>-33.5797632</v>
       </c>
       <c r="O74">
-        <v>-4.887930719999998</v>
+        <v>-5.03696448</v>
       </c>
       <c r="P74">
-        <v>-27.69827407999999</v>
+        <v>-28.54279872</v>
       </c>
       <c r="Q74">
-        <v>-25.14827407999999</v>
+        <v>-25.99279872</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1496984972019777</v>
+        <v>0.1535465896909398</v>
       </c>
       <c r="T74">
-        <v>1.902937463899314</v>
+        <v>1.973416629228919</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.0816719312456453</v>
+        <v>0.08055313766693781</v>
       </c>
       <c r="W74">
-        <v>0.1844002762058744</v>
+        <v>0.1846249299564789</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5444795416376353</v>
+        <v>0.5370209177795855</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1762337780847834</v>
+        <v>0.1777837780847834</v>
       </c>
       <c r="C75">
-        <v>-218.2068113307087</v>
+        <v>-224.5160034549883</v>
       </c>
       <c r="D75">
-        <v>117.1971886692913</v>
+        <v>115.8359965450117</v>
       </c>
       <c r="E75">
-        <v>-40.29599999999999</v>
+        <v>-35.34800000000001</v>
       </c>
       <c r="F75">
-        <v>361.204</v>
+        <v>366.152</v>
       </c>
       <c r="G75">
         <v>25.8</v>
@@ -7431,37 +7431,37 @@
         <v>38.95</v>
       </c>
       <c r="M75">
-        <v>72.5297632</v>
+        <v>73.5233216</v>
       </c>
       <c r="N75">
-        <v>-33.5797632</v>
+        <v>-34.5733216</v>
       </c>
       <c r="O75">
-        <v>-5.03696448</v>
+        <v>-5.18599824</v>
       </c>
       <c r="P75">
-        <v>-28.54279872</v>
+        <v>-29.38732336</v>
       </c>
       <c r="Q75">
-        <v>-25.99279872</v>
+        <v>-26.83732336</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1535465896909398</v>
+        <v>0.1576906892944376</v>
       </c>
       <c r="T75">
-        <v>1.973416629228919</v>
+        <v>2.049317268814646</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.08055313766693781</v>
+        <v>0.07946458175251973</v>
       </c>
       <c r="W75">
-        <v>0.1846249299564789</v>
+        <v>0.184843511984094</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5370209177795855</v>
+        <v>0.5297638783501315</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1777837780847834</v>
+        <v>0.1793337780847833</v>
       </c>
       <c r="C76">
-        <v>-224.5160034549883</v>
+        <v>-230.7939393494376</v>
       </c>
       <c r="D76">
-        <v>115.8359965450117</v>
+        <v>114.5060606505624</v>
       </c>
       <c r="E76">
-        <v>-35.34800000000001</v>
+        <v>-30.39999999999998</v>
       </c>
       <c r="F76">
-        <v>366.152</v>
+        <v>371.1</v>
       </c>
       <c r="G76">
         <v>25.8</v>
@@ -7513,37 +7513,37 @@
         <v>38.95</v>
       </c>
       <c r="M76">
-        <v>73.5233216</v>
+        <v>74.51688</v>
       </c>
       <c r="N76">
-        <v>-34.5733216</v>
+        <v>-35.56688</v>
       </c>
       <c r="O76">
-        <v>-5.18599824</v>
+        <v>-5.335031999999999</v>
       </c>
       <c r="P76">
-        <v>-29.38732336</v>
+        <v>-30.231848</v>
       </c>
       <c r="Q76">
-        <v>-26.83732336</v>
+        <v>-27.681848</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1576906892944376</v>
+        <v>0.162166316866215</v>
       </c>
       <c r="T76">
-        <v>2.049317268814646</v>
+        <v>2.131289959567233</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.07946458175251973</v>
+        <v>0.07840505399581947</v>
       </c>
       <c r="W76">
-        <v>0.184843511984094</v>
+        <v>0.1850562651576395</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5297638783501315</v>
+        <v>0.5227003599721298</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1793337780847833</v>
+        <v>0.1808837780847833</v>
       </c>
       <c r="C77">
-        <v>-230.7939393494376</v>
+        <v>-237.0416833707626</v>
       </c>
       <c r="D77">
-        <v>114.5060606505624</v>
+        <v>113.2063166292374</v>
       </c>
       <c r="E77">
-        <v>-30.39999999999998</v>
+        <v>-25.452</v>
       </c>
       <c r="F77">
-        <v>371.1</v>
+        <v>376.048</v>
       </c>
       <c r="G77">
         <v>25.8</v>
@@ -7595,37 +7595,37 @@
         <v>38.95</v>
       </c>
       <c r="M77">
-        <v>74.51688</v>
+        <v>75.5104384</v>
       </c>
       <c r="N77">
-        <v>-35.56688</v>
+        <v>-36.5604384</v>
       </c>
       <c r="O77">
-        <v>-5.335031999999999</v>
+        <v>-5.484065759999999</v>
       </c>
       <c r="P77">
-        <v>-30.231848</v>
+        <v>-31.07637264</v>
       </c>
       <c r="Q77">
-        <v>-27.681848</v>
+        <v>-28.52637263999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.162166316866215</v>
+        <v>0.1670149134023073</v>
       </c>
       <c r="T77">
-        <v>2.131289959567233</v>
+        <v>2.220093707882534</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.07840505399581947</v>
+        <v>0.07737340854850606</v>
       </c>
       <c r="W77">
-        <v>0.1850562651576395</v>
+        <v>0.18526341956346</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5227003599721298</v>
+        <v>0.5158227236567071</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1808837780847833</v>
+        <v>0.1824337780847833</v>
       </c>
       <c r="C78">
-        <v>-237.0416833707626</v>
+        <v>-243.260252092529</v>
       </c>
       <c r="D78">
-        <v>113.2063166292374</v>
+        <v>111.935747907471</v>
       </c>
       <c r="E78">
-        <v>-25.452</v>
+        <v>-20.50399999999996</v>
       </c>
       <c r="F78">
-        <v>376.048</v>
+        <v>380.996</v>
       </c>
       <c r="G78">
         <v>25.8</v>
@@ -7677,37 +7677,37 @@
         <v>38.95</v>
       </c>
       <c r="M78">
-        <v>75.5104384</v>
+        <v>76.50399680000001</v>
       </c>
       <c r="N78">
-        <v>-36.5604384</v>
+        <v>-37.55399680000001</v>
       </c>
       <c r="O78">
-        <v>-5.484065759999999</v>
+        <v>-5.633099520000001</v>
       </c>
       <c r="P78">
-        <v>-31.07637264</v>
+        <v>-31.92089728000001</v>
       </c>
       <c r="Q78">
-        <v>-28.52637263999999</v>
+        <v>-29.37089728</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1670149134023073</v>
+        <v>0.1722851270284946</v>
       </c>
       <c r="T78">
-        <v>2.220093707882534</v>
+        <v>2.316619521268731</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.07737340854850606</v>
+        <v>0.07636855908683714</v>
       </c>
       <c r="W78">
-        <v>0.18526341956346</v>
+        <v>0.1854651933353631</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5158227236567071</v>
+        <v>0.509123727245581</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1824337780847833</v>
+        <v>0.1839837780847833</v>
       </c>
       <c r="C79">
-        <v>-243.260252092529</v>
+        <v>-249.4506169568655</v>
       </c>
       <c r="D79">
-        <v>111.935747907471</v>
+        <v>110.6933830431345</v>
       </c>
       <c r="E79">
-        <v>-20.50399999999996</v>
+        <v>-15.55599999999998</v>
       </c>
       <c r="F79">
-        <v>380.996</v>
+        <v>385.944</v>
       </c>
       <c r="G79">
         <v>25.8</v>
@@ -7759,37 +7759,37 @@
         <v>38.95</v>
       </c>
       <c r="M79">
-        <v>76.50399680000001</v>
+        <v>77.49755520000001</v>
       </c>
       <c r="N79">
-        <v>-37.55399680000001</v>
+        <v>-38.54755520000001</v>
       </c>
       <c r="O79">
-        <v>-5.633099520000001</v>
+        <v>-5.782133280000001</v>
       </c>
       <c r="P79">
-        <v>-31.92089728000001</v>
+        <v>-32.76542192</v>
       </c>
       <c r="Q79">
-        <v>-29.37089728</v>
+        <v>-30.21542192</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1722851270284946</v>
+        <v>0.1780344509843353</v>
       </c>
       <c r="T79">
-        <v>2.316619521268731</v>
+        <v>2.421920408599128</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.07636855908683714</v>
+        <v>0.07538947499598027</v>
       </c>
       <c r="W79">
-        <v>0.1854651933353631</v>
+        <v>0.1856617934208072</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.509123727245581</v>
+        <v>0.5025964999732018</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1839837780847833</v>
+        <v>0.2134535623975593</v>
       </c>
       <c r="C80">
-        <v>-249.4506169568655</v>
+        <v>-273.6869906561831</v>
       </c>
       <c r="D80">
-        <v>110.6933830431345</v>
+        <v>91.40500934381693</v>
       </c>
       <c r="E80">
-        <v>-15.55599999999998</v>
+        <v>-10.60799999999995</v>
       </c>
       <c r="F80">
-        <v>385.944</v>
+        <v>390.8920000000001</v>
       </c>
       <c r="G80">
         <v>25.8</v>
@@ -7841,45 +7841,45 @@
         <v>38.95</v>
       </c>
       <c r="M80">
-        <v>77.49755520000001</v>
+        <v>92.17233360000002</v>
       </c>
       <c r="N80">
-        <v>-38.54755520000001</v>
+        <v>-53.22233360000001</v>
       </c>
       <c r="O80">
-        <v>-5.782133280000001</v>
+        <v>-7.983350040000001</v>
       </c>
       <c r="P80">
-        <v>-32.76542192</v>
+        <v>-45.23898356000001</v>
       </c>
       <c r="Q80">
-        <v>-30.21542192</v>
+        <v>-42.68898356000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1780344509843353</v>
+        <v>0.1856160168063319</v>
       </c>
       <c r="T80">
-        <v>2.421920408599128</v>
+        <v>2.560779449164936</v>
       </c>
       <c r="U80">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.07538947499598027</v>
+        <v>0.06338669936854023</v>
       </c>
       <c r="W80">
-        <v>0.1856617934208072</v>
+        <v>0.2208534162888982</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.5025964999732018</v>
+        <v>0.4225779957902682</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2134535623975593</v>
+        <v>0.2153535623975593</v>
       </c>
       <c r="C81">
-        <v>-273.6869906561831</v>
+        <v>-279.6504645178396</v>
       </c>
       <c r="D81">
-        <v>91.40500934381693</v>
+        <v>90.38953548216038</v>
       </c>
       <c r="E81">
-        <v>-10.60799999999995</v>
+        <v>-5.659999999999968</v>
       </c>
       <c r="F81">
-        <v>390.8920000000001</v>
+        <v>395.84</v>
       </c>
       <c r="G81">
         <v>25.8</v>
@@ -7923,37 +7923,37 @@
         <v>38.95</v>
       </c>
       <c r="M81">
-        <v>92.17233360000002</v>
+        <v>93.33907200000002</v>
       </c>
       <c r="N81">
-        <v>-53.22233360000001</v>
+        <v>-54.38907200000001</v>
       </c>
       <c r="O81">
-        <v>-7.983350040000001</v>
+        <v>-8.158360800000002</v>
       </c>
       <c r="P81">
-        <v>-45.23898356000001</v>
+        <v>-46.23071120000001</v>
       </c>
       <c r="Q81">
-        <v>-42.68898356000001</v>
+        <v>-43.68071120000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1856160168063319</v>
+        <v>0.1926068176466485</v>
       </c>
       <c r="T81">
-        <v>2.560779449164936</v>
+        <v>2.688818421623183</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.06338669936854023</v>
+        <v>0.06259436562643347</v>
       </c>
       <c r="W81">
-        <v>0.2208534162888982</v>
+        <v>0.221040248585287</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4225779957902682</v>
+        <v>0.4172957708428898</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2153535623975593</v>
+        <v>0.2172535623975593</v>
       </c>
       <c r="C82">
-        <v>-279.6504645178396</v>
+        <v>-285.5916232578275</v>
       </c>
       <c r="D82">
-        <v>90.38953548216038</v>
+        <v>89.39637674217259</v>
       </c>
       <c r="E82">
-        <v>-5.659999999999968</v>
+        <v>-0.7119999999999891</v>
       </c>
       <c r="F82">
-        <v>395.84</v>
+        <v>400.788</v>
       </c>
       <c r="G82">
         <v>25.8</v>
@@ -8005,37 +8005,37 @@
         <v>38.95</v>
       </c>
       <c r="M82">
-        <v>93.33907200000002</v>
+        <v>94.5058104</v>
       </c>
       <c r="N82">
-        <v>-54.38907200000001</v>
+        <v>-55.5558104</v>
       </c>
       <c r="O82">
-        <v>-8.158360800000002</v>
+        <v>-8.33337156</v>
       </c>
       <c r="P82">
-        <v>-46.23071120000001</v>
+        <v>-47.22243884</v>
       </c>
       <c r="Q82">
-        <v>-43.68071120000001</v>
+        <v>-44.67243884</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1926068176466485</v>
+        <v>0.20033349225963</v>
       </c>
       <c r="T82">
-        <v>2.688818421623183</v>
+        <v>2.830335180655982</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.06259436562643347</v>
+        <v>0.06182159568042813</v>
       </c>
       <c r="W82">
-        <v>0.221040248585287</v>
+        <v>0.2212224677385551</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4172957708428898</v>
+        <v>0.4121439712028543</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2172535623975593</v>
+        <v>0.2191535623975593</v>
       </c>
       <c r="C83">
-        <v>-285.5916232578275</v>
+        <v>-291.5111944468855</v>
       </c>
       <c r="D83">
-        <v>89.39637674217259</v>
+        <v>88.42480555311458</v>
       </c>
       <c r="E83">
-        <v>-0.7119999999999891</v>
+        <v>4.236000000000047</v>
       </c>
       <c r="F83">
-        <v>400.788</v>
+        <v>405.736</v>
       </c>
       <c r="G83">
         <v>25.8</v>
@@ -8087,37 +8087,37 @@
         <v>38.95</v>
       </c>
       <c r="M83">
-        <v>94.5058104</v>
+        <v>95.67254880000002</v>
       </c>
       <c r="N83">
-        <v>-55.5558104</v>
+        <v>-56.72254880000001</v>
       </c>
       <c r="O83">
-        <v>-8.33337156</v>
+        <v>-8.508382320000001</v>
       </c>
       <c r="P83">
-        <v>-47.22243884</v>
+        <v>-48.21416648000001</v>
       </c>
       <c r="Q83">
-        <v>-44.67243884</v>
+        <v>-45.66416648000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.20033349225963</v>
+        <v>0.2089186862740539</v>
       </c>
       <c r="T83">
-        <v>2.830335180655982</v>
+        <v>2.987576024025759</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.06182159568042813</v>
+        <v>0.06106767378188632</v>
       </c>
       <c r="W83">
-        <v>0.2212224677385551</v>
+        <v>0.2214002425222312</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4121439712028543</v>
+        <v>0.4071178252125754</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2191535623975593</v>
+        <v>0.2210535623975593</v>
       </c>
       <c r="C84">
-        <v>-291.5111944468855</v>
+        <v>-297.409874366483</v>
       </c>
       <c r="D84">
-        <v>88.42480555311458</v>
+        <v>87.47412563351705</v>
       </c>
       <c r="E84">
-        <v>4.236000000000047</v>
+        <v>9.184000000000026</v>
       </c>
       <c r="F84">
-        <v>405.736</v>
+        <v>410.684</v>
       </c>
       <c r="G84">
         <v>25.8</v>
@@ -8169,37 +8169,37 @@
         <v>38.95</v>
       </c>
       <c r="M84">
-        <v>95.67254880000002</v>
+        <v>96.83928720000002</v>
       </c>
       <c r="N84">
-        <v>-56.72254880000001</v>
+        <v>-57.88928720000001</v>
       </c>
       <c r="O84">
-        <v>-8.508382320000001</v>
+        <v>-8.683393080000002</v>
       </c>
       <c r="P84">
-        <v>-48.21416648000001</v>
+        <v>-49.20589412000001</v>
       </c>
       <c r="Q84">
-        <v>-45.66416648000001</v>
+        <v>-46.65589412000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2089186862740539</v>
+        <v>0.2185139031137042</v>
       </c>
       <c r="T84">
-        <v>2.987576024025759</v>
+        <v>3.163315790144922</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.06106767378188632</v>
+        <v>0.06033191867608045</v>
       </c>
       <c r="W84">
-        <v>0.2214002425222312</v>
+        <v>0.2215737335761802</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4071178252125754</v>
+        <v>0.4022127911738698</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2210535623975593</v>
+        <v>0.2229535623975593</v>
       </c>
       <c r="C85">
-        <v>-297.409874366483</v>
+        <v>-303.2883296729275</v>
       </c>
       <c r="D85">
-        <v>87.47412563351705</v>
+        <v>86.54367032707256</v>
       </c>
       <c r="E85">
-        <v>9.184000000000026</v>
+        <v>14.13200000000006</v>
       </c>
       <c r="F85">
-        <v>410.684</v>
+        <v>415.6320000000001</v>
       </c>
       <c r="G85">
         <v>25.8</v>
@@ -8251,37 +8251,37 @@
         <v>38.95</v>
       </c>
       <c r="M85">
-        <v>96.83928720000002</v>
+        <v>98.00602560000002</v>
       </c>
       <c r="N85">
-        <v>-57.88928720000001</v>
+        <v>-59.05602560000001</v>
       </c>
       <c r="O85">
-        <v>-8.683393080000002</v>
+        <v>-8.858403840000001</v>
       </c>
       <c r="P85">
-        <v>-49.20589412000001</v>
+        <v>-50.19762176000001</v>
       </c>
       <c r="Q85">
-        <v>-46.65589412000001</v>
+        <v>-47.64762176000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2185139031137042</v>
+        <v>0.2293085220583107</v>
       </c>
       <c r="T85">
-        <v>3.163315790144922</v>
+        <v>3.36102302702898</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.06033191867608045</v>
+        <v>0.05961368154898426</v>
       </c>
       <c r="W85">
-        <v>0.2215737335761802</v>
+        <v>0.2217430938907495</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4022127911738698</v>
+        <v>0.3974245436598951</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2229535623975593</v>
+        <v>0.2248535623975593</v>
       </c>
       <c r="C86">
-        <v>-303.2883296729274</v>
+        <v>-309.1471989563834</v>
       </c>
       <c r="D86">
-        <v>86.5436703270726</v>
+        <v>85.6328010436166</v>
       </c>
       <c r="E86">
-        <v>14.13200000000001</v>
+        <v>19.07999999999998</v>
       </c>
       <c r="F86">
-        <v>415.632</v>
+        <v>420.58</v>
       </c>
       <c r="G86">
         <v>25.8</v>
@@ -8333,37 +8333,37 @@
         <v>38.95</v>
       </c>
       <c r="M86">
-        <v>98.0060256</v>
+        <v>99.172764</v>
       </c>
       <c r="N86">
-        <v>-59.0560256</v>
+        <v>-60.222764</v>
       </c>
       <c r="O86">
-        <v>-8.858403839999999</v>
+        <v>-9.033414599999999</v>
       </c>
       <c r="P86">
-        <v>-50.19762176</v>
+        <v>-51.1893494</v>
       </c>
       <c r="Q86">
-        <v>-47.64762176</v>
+        <v>-48.6393494</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2293085220583105</v>
+        <v>0.2415424235288646</v>
       </c>
       <c r="T86">
-        <v>3.361023027028977</v>
+        <v>3.585091228830909</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.05961368154898427</v>
+        <v>0.05891234411899622</v>
       </c>
       <c r="W86">
-        <v>0.2217430938907495</v>
+        <v>0.2219084692567407</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3974245436598951</v>
+        <v>0.3927489607933081</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2248535623975593</v>
+        <v>0.2267535623975593</v>
       </c>
       <c r="C87">
-        <v>-309.1471989563834</v>
+        <v>-314.9870942024655</v>
       </c>
       <c r="D87">
-        <v>85.6328010436166</v>
+        <v>84.74090579753455</v>
       </c>
       <c r="E87">
-        <v>19.07999999999998</v>
+        <v>24.02800000000002</v>
       </c>
       <c r="F87">
-        <v>420.58</v>
+        <v>425.528</v>
       </c>
       <c r="G87">
         <v>25.8</v>
@@ -8415,37 +8415,37 @@
         <v>38.95</v>
       </c>
       <c r="M87">
-        <v>99.172764</v>
+        <v>100.3395024</v>
       </c>
       <c r="N87">
-        <v>-60.222764</v>
+        <v>-61.38950240000001</v>
       </c>
       <c r="O87">
-        <v>-9.033414599999999</v>
+        <v>-9.208425360000001</v>
       </c>
       <c r="P87">
-        <v>-51.1893494</v>
+        <v>-52.18107704000001</v>
       </c>
       <c r="Q87">
-        <v>-48.6393494</v>
+        <v>-49.63107704000002</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2415424235288646</v>
+        <v>0.2555240252094977</v>
       </c>
       <c r="T87">
-        <v>3.585091228830909</v>
+        <v>3.841169173747403</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.05891234411899622</v>
+        <v>0.05822731686179859</v>
       </c>
       <c r="W87">
-        <v>0.2219084692567407</v>
+        <v>0.2220699986839879</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3927489607933081</v>
+        <v>0.3881821124119905</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2267535623975593</v>
+        <v>0.2286535623975593</v>
       </c>
       <c r="C88">
-        <v>-314.9870942024655</v>
+        <v>-320.8086021634348</v>
       </c>
       <c r="D88">
-        <v>84.74090579753455</v>
+        <v>83.86739783656516</v>
       </c>
       <c r="E88">
-        <v>24.02800000000002</v>
+        <v>28.976</v>
       </c>
       <c r="F88">
-        <v>425.528</v>
+        <v>430.476</v>
       </c>
       <c r="G88">
         <v>25.8</v>
@@ -8497,37 +8497,37 @@
         <v>38.95</v>
       </c>
       <c r="M88">
-        <v>100.3395024</v>
+        <v>101.5062408</v>
       </c>
       <c r="N88">
-        <v>-61.38950240000001</v>
+        <v>-62.5562408</v>
       </c>
       <c r="O88">
-        <v>-9.208425360000001</v>
+        <v>-9.383436119999999</v>
       </c>
       <c r="P88">
-        <v>-52.18107704000001</v>
+        <v>-53.17280468</v>
       </c>
       <c r="Q88">
-        <v>-49.63107704000002</v>
+        <v>-50.62280468</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2555240252094977</v>
+        <v>0.2716566425333053</v>
       </c>
       <c r="T88">
-        <v>3.841169173747403</v>
+        <v>4.136643725574126</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05822731686179859</v>
+        <v>0.05755803735763999</v>
       </c>
       <c r="W88">
-        <v>0.2220699986839879</v>
+        <v>0.2222278147910685</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3881821124119905</v>
+        <v>0.3837202490509333</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2286535623975593</v>
+        <v>0.2305535623975593</v>
       </c>
       <c r="C89">
-        <v>-320.8086021634348</v>
+        <v>-326.6122856454554</v>
       </c>
       <c r="D89">
-        <v>83.86739783656516</v>
+        <v>83.01171435454461</v>
       </c>
       <c r="E89">
-        <v>28.976</v>
+        <v>33.92400000000004</v>
       </c>
       <c r="F89">
-        <v>430.476</v>
+        <v>435.424</v>
       </c>
       <c r="G89">
         <v>25.8</v>
@@ -8579,37 +8579,37 @@
         <v>38.95</v>
       </c>
       <c r="M89">
-        <v>101.5062408</v>
+        <v>102.6729792</v>
       </c>
       <c r="N89">
-        <v>-62.5562408</v>
+        <v>-63.72297920000001</v>
       </c>
       <c r="O89">
-        <v>-9.383436119999999</v>
+        <v>-9.558446880000002</v>
       </c>
       <c r="P89">
-        <v>-53.17280468</v>
+        <v>-54.16453232000001</v>
       </c>
       <c r="Q89">
-        <v>-50.62280468</v>
+        <v>-51.61453232000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2716566425333053</v>
+        <v>0.2904780294110808</v>
       </c>
       <c r="T89">
-        <v>4.136643725574126</v>
+        <v>4.481364036038637</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.05755803735763999</v>
+        <v>0.05690396875130316</v>
       </c>
       <c r="W89">
-        <v>0.2222278147910685</v>
+        <v>0.2223820441684427</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3837202490509333</v>
+        <v>0.3793597916753544</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2305535623975593</v>
+        <v>0.2324535623975593</v>
       </c>
       <c r="C90">
-        <v>-326.6122856454554</v>
+        <v>-332.3986847178438</v>
       </c>
       <c r="D90">
-        <v>83.01171435454461</v>
+        <v>82.17331528215618</v>
       </c>
       <c r="E90">
-        <v>33.92400000000004</v>
+        <v>38.87200000000001</v>
       </c>
       <c r="F90">
-        <v>435.424</v>
+        <v>440.372</v>
       </c>
       <c r="G90">
         <v>25.8</v>
@@ -8661,37 +8661,37 @@
         <v>38.95</v>
       </c>
       <c r="M90">
-        <v>102.6729792</v>
+        <v>103.8397176</v>
       </c>
       <c r="N90">
-        <v>-63.72297920000001</v>
+        <v>-64.88971760000001</v>
       </c>
       <c r="O90">
-        <v>-9.558446880000002</v>
+        <v>-9.733457640000001</v>
       </c>
       <c r="P90">
-        <v>-54.16453232000001</v>
+        <v>-55.15625996000001</v>
       </c>
       <c r="Q90">
-        <v>-51.61453232000001</v>
+        <v>-52.60625996000002</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2904780294110808</v>
+        <v>0.3127214866302699</v>
       </c>
       <c r="T90">
-        <v>4.481364036038637</v>
+        <v>4.888760766587605</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05690396875130316</v>
+        <v>0.05626459831589526</v>
       </c>
       <c r="W90">
-        <v>0.2223820441684427</v>
+        <v>0.2225328077171119</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3793597916753544</v>
+        <v>0.3750973221059685</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2324535623975593</v>
+        <v>0.2343535623975593</v>
       </c>
       <c r="C91">
-        <v>-332.3986847178438</v>
+        <v>-338.1683178497736</v>
       </c>
       <c r="D91">
-        <v>82.17331528215618</v>
+        <v>81.35168215022632</v>
       </c>
       <c r="E91">
-        <v>38.87200000000001</v>
+        <v>43.81999999999999</v>
       </c>
       <c r="F91">
-        <v>440.372</v>
+        <v>445.32</v>
       </c>
       <c r="G91">
         <v>25.8</v>
@@ -8743,37 +8743,37 @@
         <v>38.95</v>
       </c>
       <c r="M91">
-        <v>103.8397176</v>
+        <v>105.006456</v>
       </c>
       <c r="N91">
-        <v>-64.88971760000001</v>
+        <v>-66.056456</v>
       </c>
       <c r="O91">
-        <v>-9.733457640000001</v>
+        <v>-9.908468399999999</v>
       </c>
       <c r="P91">
-        <v>-55.15625996000001</v>
+        <v>-56.1479876</v>
       </c>
       <c r="Q91">
-        <v>-52.60625996000002</v>
+        <v>-53.5979876</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3127214866302699</v>
+        <v>0.339413635293297</v>
       </c>
       <c r="T91">
-        <v>4.888760766587605</v>
+        <v>5.377636843246366</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05626459831589526</v>
+        <v>0.05563943611238532</v>
       </c>
       <c r="W91">
-        <v>0.2225328077171119</v>
+        <v>0.2226802209646996</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3750973221059685</v>
+        <v>0.3709295740825688</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2343535623975593</v>
+        <v>0.2362535623975593</v>
       </c>
       <c r="C92">
-        <v>-338.1683178497736</v>
+        <v>-343.9216829794604</v>
       </c>
       <c r="D92">
-        <v>81.35168215022632</v>
+        <v>80.54631702053962</v>
       </c>
       <c r="E92">
-        <v>43.81999999999999</v>
+        <v>48.76800000000003</v>
       </c>
       <c r="F92">
-        <v>445.32</v>
+        <v>450.268</v>
       </c>
       <c r="G92">
         <v>25.8</v>
@@ -8825,37 +8825,37 @@
         <v>38.95</v>
       </c>
       <c r="M92">
-        <v>105.006456</v>
+        <v>106.1731944</v>
       </c>
       <c r="N92">
-        <v>-66.056456</v>
+        <v>-67.22319440000001</v>
       </c>
       <c r="O92">
-        <v>-9.908468399999999</v>
+        <v>-10.08347916</v>
       </c>
       <c r="P92">
-        <v>-56.1479876</v>
+        <v>-57.13971524000001</v>
       </c>
       <c r="Q92">
-        <v>-53.5979876</v>
+        <v>-54.58971524000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.339413635293297</v>
+        <v>0.3720373725481078</v>
       </c>
       <c r="T92">
-        <v>5.377636843246366</v>
+        <v>5.975152048051518</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05563943611238532</v>
+        <v>0.05502801373752394</v>
       </c>
       <c r="W92">
-        <v>0.2226802209646996</v>
+        <v>0.2228243943606918</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3709295740825688</v>
+        <v>0.3668534249168263</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2362535623975593</v>
+        <v>0.2381535623975593</v>
       </c>
       <c r="C93">
-        <v>-343.9216829794604</v>
+        <v>-349.6592585204608</v>
       </c>
       <c r="D93">
-        <v>80.54631702053962</v>
+        <v>79.75674147953924</v>
       </c>
       <c r="E93">
-        <v>48.76800000000003</v>
+        <v>53.71600000000001</v>
       </c>
       <c r="F93">
-        <v>450.268</v>
+        <v>455.216</v>
       </c>
       <c r="G93">
         <v>25.8</v>
@@ -8907,37 +8907,37 @@
         <v>38.95</v>
       </c>
       <c r="M93">
-        <v>106.1731944</v>
+        <v>107.3399328</v>
       </c>
       <c r="N93">
-        <v>-67.22319440000001</v>
+        <v>-68.3899328</v>
       </c>
       <c r="O93">
-        <v>-10.08347916</v>
+        <v>-10.25848992</v>
       </c>
       <c r="P93">
-        <v>-57.13971524000001</v>
+        <v>-58.13144287999999</v>
       </c>
       <c r="Q93">
-        <v>-54.58971524000001</v>
+        <v>-55.58144288</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3720373725481078</v>
+        <v>0.4128170441166213</v>
       </c>
       <c r="T93">
-        <v>5.975152048051518</v>
+        <v>6.72204605405796</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05502801373752394</v>
+        <v>0.05442988315342042</v>
       </c>
       <c r="W93">
-        <v>0.2228243943606918</v>
+        <v>0.2229654335524235</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3668534249168263</v>
+        <v>0.3628658876894695</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2381535623975593</v>
+        <v>0.2400535623975593</v>
       </c>
       <c r="C94">
-        <v>-349.6592585204608</v>
+        <v>-355.3815043093601</v>
       </c>
       <c r="D94">
-        <v>79.75674147953924</v>
+        <v>78.98249569063995</v>
       </c>
       <c r="E94">
-        <v>53.71600000000001</v>
+        <v>58.66400000000004</v>
       </c>
       <c r="F94">
-        <v>455.216</v>
+        <v>460.164</v>
       </c>
       <c r="G94">
         <v>25.8</v>
@@ -8989,37 +8989,37 @@
         <v>38.95</v>
       </c>
       <c r="M94">
-        <v>107.3399328</v>
+        <v>108.5066712</v>
       </c>
       <c r="N94">
-        <v>-68.3899328</v>
+        <v>-69.55667120000001</v>
       </c>
       <c r="O94">
-        <v>-10.25848992</v>
+        <v>-10.43350068</v>
       </c>
       <c r="P94">
-        <v>-58.13144287999999</v>
+        <v>-59.12317052000001</v>
       </c>
       <c r="Q94">
-        <v>-55.58144288</v>
+        <v>-56.57317052000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4128170441166213</v>
+        <v>0.4652480504189959</v>
       </c>
       <c r="T94">
-        <v>6.72204605405796</v>
+        <v>7.682338347494811</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05442988315342042</v>
+        <v>0.05384461559263095</v>
       </c>
       <c r="W94">
-        <v>0.2229654335524235</v>
+        <v>0.2231034396432576</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3628658876894695</v>
+        <v>0.358964103950873</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2400535623975593</v>
+        <v>0.2419535623975593</v>
       </c>
       <c r="C95">
-        <v>-355.3815043093601</v>
+        <v>-361.0888624987908</v>
       </c>
       <c r="D95">
-        <v>78.98249569063995</v>
+        <v>78.22313750120917</v>
       </c>
       <c r="E95">
-        <v>58.66400000000004</v>
+        <v>63.61200000000002</v>
       </c>
       <c r="F95">
-        <v>460.164</v>
+        <v>465.112</v>
       </c>
       <c r="G95">
         <v>25.8</v>
@@ -9071,37 +9071,37 @@
         <v>38.95</v>
       </c>
       <c r="M95">
-        <v>108.5066712</v>
+        <v>109.6734096</v>
       </c>
       <c r="N95">
-        <v>-69.55667120000001</v>
+        <v>-70.72340960000001</v>
       </c>
       <c r="O95">
-        <v>-10.43350068</v>
+        <v>-10.60851144</v>
       </c>
       <c r="P95">
-        <v>-59.12317052000001</v>
+        <v>-60.11489816000001</v>
       </c>
       <c r="Q95">
-        <v>-56.57317052000001</v>
+        <v>-57.56489816000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4652480504189959</v>
+        <v>0.535156058822162</v>
       </c>
       <c r="T95">
-        <v>7.682338347494811</v>
+        <v>8.962728072077283</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05384461559263095</v>
+        <v>0.05327180053313487</v>
       </c>
       <c r="W95">
-        <v>0.2231034396432576</v>
+        <v>0.2232385094342868</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.358964103950873</v>
+        <v>0.3551453368875659</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2419535623975593</v>
+        <v>0.2438535623975593</v>
       </c>
       <c r="C96">
-        <v>-361.0888624987908</v>
+        <v>-366.7817583994286</v>
       </c>
       <c r="D96">
-        <v>78.22313750120917</v>
+        <v>77.47824160057151</v>
       </c>
       <c r="E96">
-        <v>63.61200000000002</v>
+        <v>68.56000000000006</v>
       </c>
       <c r="F96">
-        <v>465.112</v>
+        <v>470.0600000000001</v>
       </c>
       <c r="G96">
         <v>25.8</v>
@@ -9153,37 +9153,37 @@
         <v>38.95</v>
       </c>
       <c r="M96">
-        <v>109.6734096</v>
+        <v>110.840148</v>
       </c>
       <c r="N96">
-        <v>-70.72340960000001</v>
+        <v>-71.89014800000001</v>
       </c>
       <c r="O96">
-        <v>-10.60851144</v>
+        <v>-10.7835222</v>
       </c>
       <c r="P96">
-        <v>-60.11489816000001</v>
+        <v>-61.10662580000001</v>
       </c>
       <c r="Q96">
-        <v>-57.56489816000001</v>
+        <v>-58.55662580000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.535156058822162</v>
+        <v>0.6330272705865946</v>
       </c>
       <c r="T96">
-        <v>8.962728072077283</v>
+        <v>10.75527368649274</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05327180053313487</v>
+        <v>0.05271104473804925</v>
       </c>
       <c r="W96">
-        <v>0.2232385094342868</v>
+        <v>0.223370735650768</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3551453368875659</v>
+        <v>0.3514069649203283</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2438535623975593</v>
+        <v>0.2457535623975593</v>
       </c>
       <c r="C97">
-        <v>-366.7817583994286</v>
+        <v>-372.460601274332</v>
       </c>
       <c r="D97">
-        <v>77.47824160057151</v>
+        <v>76.74739872566805</v>
       </c>
       <c r="E97">
-        <v>68.56000000000006</v>
+        <v>73.50800000000004</v>
       </c>
       <c r="F97">
-        <v>470.0600000000001</v>
+        <v>475.008</v>
       </c>
       <c r="G97">
         <v>25.8</v>
@@ -9235,37 +9235,37 @@
         <v>38.95</v>
       </c>
       <c r="M97">
-        <v>110.840148</v>
+        <v>112.0068864</v>
       </c>
       <c r="N97">
-        <v>-71.89014800000001</v>
+        <v>-73.05688640000001</v>
       </c>
       <c r="O97">
-        <v>-10.7835222</v>
+        <v>-10.95853296</v>
       </c>
       <c r="P97">
-        <v>-61.10662580000001</v>
+        <v>-62.09835344000001</v>
       </c>
       <c r="Q97">
-        <v>-58.55662580000001</v>
+        <v>-59.54835344000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6330272705865946</v>
+        <v>0.7798340882332435</v>
       </c>
       <c r="T97">
-        <v>10.75527368649274</v>
+        <v>13.44409210811594</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05271104473804925</v>
+        <v>0.05216197135536123</v>
       </c>
       <c r="W97">
-        <v>0.223370735650768</v>
+        <v>0.2235002071544058</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3514069649203283</v>
+        <v>0.3477464757024082</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2457535623975593</v>
+        <v>0.2476535623975593</v>
       </c>
       <c r="C98">
-        <v>-372.4606012743319</v>
+        <v>-378.125785088747</v>
       </c>
       <c r="D98">
-        <v>76.74739872566805</v>
+        <v>76.03021491125301</v>
       </c>
       <c r="E98">
-        <v>73.50799999999998</v>
+        <v>78.45600000000002</v>
       </c>
       <c r="F98">
-        <v>475.008</v>
+        <v>479.956</v>
       </c>
       <c r="G98">
         <v>25.8</v>
@@ -9317,37 +9317,37 @@
         <v>38.95</v>
       </c>
       <c r="M98">
-        <v>112.0068864</v>
+        <v>113.1736248</v>
       </c>
       <c r="N98">
-        <v>-73.0568864</v>
+        <v>-74.22362480000001</v>
       </c>
       <c r="O98">
-        <v>-10.95853296</v>
+        <v>-11.13354372</v>
       </c>
       <c r="P98">
-        <v>-62.09835344</v>
+        <v>-63.09008108000001</v>
       </c>
       <c r="Q98">
-        <v>-59.54835344</v>
+        <v>-60.54008108000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7798340882332416</v>
+        <v>1.024512117644322</v>
       </c>
       <c r="T98">
-        <v>13.4440921081159</v>
+        <v>17.92545614415453</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05216197135536123</v>
+        <v>0.0516242190733472</v>
       </c>
       <c r="W98">
-        <v>0.2235002071544058</v>
+        <v>0.2236270091425047</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3477464757024082</v>
+        <v>0.3441614604889813</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2476535623975593</v>
+        <v>0.2495535623975593</v>
       </c>
       <c r="C99">
-        <v>-378.125785088747</v>
+        <v>-383.7776892182585</v>
       </c>
       <c r="D99">
-        <v>76.03021491125301</v>
+        <v>75.32631078174151</v>
       </c>
       <c r="E99">
-        <v>78.45600000000002</v>
+        <v>83.404</v>
       </c>
       <c r="F99">
-        <v>479.956</v>
+        <v>484.904</v>
       </c>
       <c r="G99">
         <v>25.8</v>
@@ -9399,37 +9399,37 @@
         <v>38.95</v>
       </c>
       <c r="M99">
-        <v>113.1736248</v>
+        <v>114.3403632</v>
       </c>
       <c r="N99">
-        <v>-74.22362480000001</v>
+        <v>-75.3903632</v>
       </c>
       <c r="O99">
-        <v>-11.13354372</v>
+        <v>-11.30855448</v>
       </c>
       <c r="P99">
-        <v>-63.09008108000001</v>
+        <v>-64.08180872</v>
       </c>
       <c r="Q99">
-        <v>-60.54008108000001</v>
+        <v>-61.53180872</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.024512117644322</v>
+        <v>1.513868176466483</v>
       </c>
       <c r="T99">
-        <v>17.92545614415453</v>
+        <v>26.8881842162318</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.0516242190733472</v>
+        <v>0.0510974413277008</v>
       </c>
       <c r="W99">
-        <v>0.2236270091425047</v>
+        <v>0.2237512233349282</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3441614604889813</v>
+        <v>0.3406496088513387</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2495535623975593</v>
+        <v>0.2514535623975593</v>
       </c>
       <c r="C100">
-        <v>-383.7776892182585</v>
+        <v>-389.4166791179662</v>
       </c>
       <c r="D100">
-        <v>75.32631078174151</v>
+        <v>74.63532088203385</v>
       </c>
       <c r="E100">
-        <v>83.404</v>
+        <v>88.35200000000003</v>
       </c>
       <c r="F100">
-        <v>484.904</v>
+        <v>489.852</v>
       </c>
       <c r="G100">
         <v>25.8</v>
@@ -9481,37 +9481,37 @@
         <v>38.95</v>
       </c>
       <c r="M100">
-        <v>114.3403632</v>
+        <v>115.5071016</v>
       </c>
       <c r="N100">
-        <v>-75.3903632</v>
+        <v>-76.55710160000001</v>
       </c>
       <c r="O100">
-        <v>-11.30855448</v>
+        <v>-11.48356524</v>
       </c>
       <c r="P100">
-        <v>-64.08180872</v>
+        <v>-65.07353636000001</v>
       </c>
       <c r="Q100">
-        <v>-61.53180872</v>
+        <v>-62.52353636000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.513868176466483</v>
+        <v>2.981936352932967</v>
       </c>
       <c r="T100">
-        <v>26.8881842162318</v>
+        <v>53.7763684324636</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0510974413277008</v>
+        <v>0.05058130555671392</v>
       </c>
       <c r="W100">
-        <v>0.2237512233349282</v>
+        <v>0.2238729281497269</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3406496088513387</v>
+        <v>0.3372087037114262</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2514535623975593</v>
-      </c>
-      <c r="C101">
-        <v>-389.4166791179662</v>
-      </c>
-      <c r="D101">
-        <v>74.63532088203385</v>
-      </c>
-      <c r="E101">
-        <v>88.35200000000003</v>
-      </c>
-      <c r="F101">
-        <v>489.852</v>
-      </c>
-      <c r="G101">
-        <v>25.8</v>
-      </c>
-      <c r="H101">
-        <v>93.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>41.5</v>
-      </c>
-      <c r="K101">
-        <v>2.55</v>
-      </c>
-      <c r="L101">
-        <v>38.95</v>
-      </c>
-      <c r="M101">
-        <v>115.5071016</v>
-      </c>
-      <c r="N101">
-        <v>-76.55710160000001</v>
-      </c>
-      <c r="O101">
-        <v>-11.48356524</v>
-      </c>
-      <c r="P101">
-        <v>-65.07353636000001</v>
-      </c>
-      <c r="Q101">
-        <v>-62.52353636000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.981936352932967</v>
-      </c>
-      <c r="T101">
-        <v>53.7763684324636</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05058130555671392</v>
-      </c>
-      <c r="W101">
-        <v>0.2238729281497269</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3372087037114262</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
